--- a/web-app/src/main/resources/static/amazon/Produktkuerzel Aktuell.xlsx
+++ b/web-app/src/main/resources/static/amazon/Produktkuerzel Aktuell.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\0-PfS\Produktdaten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E9BCB9-63D8-4635-85BF-DCF3C0EBBA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF4AA6D-C331-45BF-9AFD-A8ED755237BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produktmaße+Kürzel" sheetId="1" r:id="rId1"/>
     <sheet name="Produktmaße+Kürzel-alt" sheetId="2" r:id="rId2"/>
     <sheet name="Kartons" sheetId="3" r:id="rId3"/>
     <sheet name="Kartons (2)" sheetId="4" r:id="rId4"/>
-    <sheet name="Tabelle3" sheetId="5" r:id="rId5"/>
+    <sheet name="Produktmaße" sheetId="5" r:id="rId5"/>
+    <sheet name="Palettenmaße" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="863">
   <si>
     <t>Einstreu</t>
   </si>
@@ -771,9 +772,6 @@
     <t>HORSEDREAM POWER-LIN 19 kg</t>
   </si>
   <si>
-    <t>88x40x25</t>
-  </si>
-  <si>
     <t>PL</t>
   </si>
   <si>
@@ -2193,9 +2191,6 @@
     <t>Robusan</t>
   </si>
   <si>
-    <t>GlyxWie</t>
-  </si>
-  <si>
     <t>Zink Li</t>
   </si>
   <si>
@@ -2223,9 +2218,6 @@
     <t>Knobliz</t>
   </si>
   <si>
-    <t>Irish M</t>
-  </si>
-  <si>
     <t>Glyx Ma</t>
   </si>
   <si>
@@ -2515,6 +2507,129 @@
   </si>
   <si>
     <t>High Performer 10 kg</t>
+  </si>
+  <si>
+    <t>01.10002</t>
+  </si>
+  <si>
+    <t>HempFlax Hemparade, 14kg x 30 = 420 kg / 1 Palette</t>
+  </si>
+  <si>
+    <t>01.45014-30</t>
+  </si>
+  <si>
+    <t>BioBase 14 kg x 30 = 420 kg / 1 Palette</t>
+  </si>
+  <si>
+    <t>01.45014B-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boxengold  Kleintiereinstreu Premium Ecostreu  20 kg*24=480 ROT / 1 Palette </t>
+  </si>
+  <si>
+    <t>01.9011-24</t>
+  </si>
+  <si>
+    <t>HORSEDREAM Power-Hemp Classic, 360 kg  / 1 Palette</t>
+  </si>
+  <si>
+    <t>02.10002-18B</t>
+  </si>
+  <si>
+    <t>HORSEDREAM Power-Hemp Super 20*18=360 kg  / 1 Palette</t>
+  </si>
+  <si>
+    <t>HORSEDREAM Power-Lin, 19 kg x 30 = 570 kg / Palette</t>
+  </si>
+  <si>
+    <t>EURO-lin aus Leinstroh - 20 kg * 20 = 400 kg / Palette</t>
+  </si>
+  <si>
+    <t>01.10070-20</t>
+  </si>
+  <si>
+    <t>HORSEDREAM  LEIN-STROXXEL, 400 kg  / 1 Palette</t>
+  </si>
+  <si>
+    <t>02.10001/400kg</t>
+  </si>
+  <si>
+    <t>Equi-LIN 19 kg x 30 / Palette</t>
+  </si>
+  <si>
+    <t>01.10095-30</t>
+  </si>
+  <si>
+    <t>AGH Sägemehl 18kg x 30 Sack 540kg / 1 Palette</t>
+  </si>
+  <si>
+    <t>AGH Classic, 24kg x 15 Sack, 360 kg / 1 Palette 10008/24</t>
+  </si>
+  <si>
+    <t>AGH German Horse Bioaktiv, 24kg x 15 Sack 360kg / 1 Palette</t>
+  </si>
+  <si>
+    <t>Waldgold Waldboden-Einstreu (3060 l, 60 l x 51 Sack)  / 1 Palette</t>
+  </si>
+  <si>
+    <t>1300x900x1900</t>
+  </si>
+  <si>
+    <t>1200x800x2300</t>
+  </si>
+  <si>
+    <t>1200x1000x2300</t>
+  </si>
+  <si>
+    <t>29x41x15</t>
+  </si>
+  <si>
+    <t>05.1000/600</t>
+  </si>
+  <si>
+    <t>05.1000/580</t>
+  </si>
+  <si>
+    <t>01.41001-60-4</t>
+  </si>
+  <si>
+    <t>Waldgold - EINSTREU 60 L-Sack 2x2er Pack</t>
+  </si>
+  <si>
+    <t>01.30002X</t>
+  </si>
+  <si>
+    <t>AGH Xtreme 17 kg</t>
+  </si>
+  <si>
+    <t>Axt17</t>
+  </si>
+  <si>
+    <t>GlyxWieT</t>
+  </si>
+  <si>
+    <t>Irish M 7,5</t>
+  </si>
+  <si>
+    <t>Irish M 5</t>
+  </si>
+  <si>
+    <t>KAMBIO Nadelholzbriketts ohne Loch (20 kg)</t>
+  </si>
+  <si>
+    <t>KAMBIO</t>
+  </si>
+  <si>
+    <t>01.40002/oL-2</t>
+  </si>
+  <si>
+    <t>01.41001-16-2</t>
+  </si>
+  <si>
+    <t>01.41001-16-3</t>
+  </si>
+  <si>
+    <t>01.41001-16-4</t>
   </si>
 </sst>
 </file>
@@ -2524,7 +2639,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2602,8 +2717,29 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2700,8 +2836,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="33">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -3087,11 +3235,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3653,6 +3815,77 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3708,7 +3941,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3972,13 +4206,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:J282"/>
+  <dimension ref="A1:J288"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" style="10" customWidth="1"/>
     <col min="2" max="2" width="58.42578125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="11" hidden="1" customWidth="1"/>
-    <col min="4" max="5" width="7.7109375" style="11" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="11" customWidth="1"/>
+    <col min="4" max="5" width="7.7109375" style="11" customWidth="1"/>
     <col min="6" max="6" width="11.140625" style="11" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="11" customWidth="1"/>
     <col min="8" max="8" width="24.140625" style="7" customWidth="1"/>
@@ -3986,18 +4220,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="216" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="191"/>
-      <c r="C1" s="191"/>
-      <c r="D1" s="191"/>
-      <c r="E1" s="191"/>
-      <c r="F1" s="191"/>
-      <c r="G1" s="191"/>
-      <c r="H1" s="191"/>
-      <c r="I1" s="191"/>
-      <c r="J1" s="191"/>
+      <c r="B1" s="216"/>
+      <c r="C1" s="216"/>
+      <c r="D1" s="216"/>
+      <c r="E1" s="216"/>
+      <c r="F1" s="216"/>
+      <c r="G1" s="216"/>
+      <c r="H1" s="216"/>
+      <c r="I1" s="216"/>
+      <c r="J1" s="216"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -4188,26 +4422,24 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="C9" s="27"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
       <c r="F9" s="23" t="s">
-        <v>792</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>261</v>
-      </c>
+        <v>789</v>
+      </c>
+      <c r="G9" s="23"/>
       <c r="I9" s="24"/>
       <c r="J9" s="24"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>37</v>
@@ -4299,7 +4531,7 @@
       <c r="D13" s="22"/>
       <c r="E13" s="22"/>
       <c r="F13" s="23" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G13" s="23" t="s">
         <v>122</v>
@@ -4363,7 +4595,7 @@
       <c r="D16" s="29"/>
       <c r="E16" s="22"/>
       <c r="F16" s="23" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G16" s="23"/>
       <c r="H16" s="7"/>
@@ -4499,7 +4731,7 @@
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
       <c r="F22" s="23" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G22" s="23" t="s">
         <v>15</v>
@@ -4659,20 +4891,22 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="70" t="s">
+        <v>688</v>
+      </c>
+      <c r="B30" s="187" t="s">
         <v>689</v>
-      </c>
-      <c r="B30" s="187" t="s">
-        <v>690</v>
       </c>
       <c r="C30" s="188"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="23" t="s">
-        <v>691</v>
-      </c>
-      <c r="G30" s="23"/>
+        <v>690</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="H30" s="189" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="I30" s="24"/>
       <c r="J30" s="24"/>
@@ -4707,62 +4941,74 @@
       </c>
       <c r="J31" s="24"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
+    <row r="32" spans="1:10" s="212" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="205" t="s">
         <v>107</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="207" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="208">
         <v>27</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="208">
         <v>21</v>
       </c>
-      <c r="F32" s="23" t="s">
-        <v>695</v>
-      </c>
-      <c r="G32" s="23" t="s">
+      <c r="F32" s="209" t="s">
+        <v>694</v>
+      </c>
+      <c r="G32" s="209" t="s">
         <v>29</v>
       </c>
-      <c r="I32" s="24">
+      <c r="H32" s="210"/>
+      <c r="I32" s="211">
         <v>8</v>
       </c>
-      <c r="J32" s="24"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
+      <c r="J32" s="211"/>
+    </row>
+    <row r="33" spans="1:10" s="212" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="205" t="s">
+        <v>851</v>
+      </c>
+      <c r="B33" s="206" t="s">
+        <v>852</v>
+      </c>
+      <c r="C33" s="207" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="208">
+        <v>27</v>
+      </c>
+      <c r="E33" s="208">
+        <v>21</v>
+      </c>
+      <c r="F33" s="209" t="s">
+        <v>853</v>
+      </c>
+      <c r="G33" s="209" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="210"/>
+      <c r="I33" s="211">
+        <v>8</v>
+      </c>
+      <c r="J33" s="211"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B34" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="G33" s="23"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
-        <v>614</v>
-      </c>
-      <c r="B34" s="185" t="s">
-        <v>688</v>
-      </c>
-      <c r="C34" s="186"/>
+      <c r="C34" s="32"/>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
       <c r="F34" s="23" t="s">
-        <v>696</v>
+        <v>112</v>
       </c>
       <c r="G34" s="23"/>
       <c r="I34" s="24"/>
@@ -4770,596 +5016,597 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="B35" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>115</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="B35" s="185" t="s">
+        <v>687</v>
+      </c>
+      <c r="C35" s="186"/>
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
       <c r="F35" s="23" t="s">
-        <v>697</v>
-      </c>
-      <c r="G35" s="23" t="s">
-        <v>812</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>117</v>
-      </c>
+        <v>695</v>
+      </c>
+      <c r="G35" s="23"/>
       <c r="I35" s="24"/>
       <c r="J35" s="24"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="B36" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="C36" s="44"/>
+      <c r="A36" s="70" t="s">
+        <v>859</v>
+      </c>
+      <c r="B36" s="213" t="s">
+        <v>857</v>
+      </c>
+      <c r="C36" s="214"/>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
       <c r="F36" s="23" t="s">
-        <v>698</v>
+        <v>858</v>
       </c>
       <c r="G36" s="23" t="s">
-        <v>47</v>
+        <v>122</v>
+      </c>
+      <c r="H36" s="215" t="s">
+        <v>858</v>
       </c>
       <c r="I36" s="24"/>
       <c r="J36" s="24"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="B37" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="C37" s="44"/>
+        <v>113</v>
+      </c>
+      <c r="B37" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>115</v>
+      </c>
       <c r="D37" s="22"/>
       <c r="E37" s="22"/>
       <c r="F37" s="23" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>122</v>
+        <v>809</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="I37" s="24"/>
       <c r="J37" s="24"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
-        <v>123</v>
+        <v>860</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C38" s="44"/>
       <c r="D38" s="22"/>
       <c r="E38" s="22"/>
       <c r="F38" s="23" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="G38" s="23" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="I38" s="24"/>
       <c r="J38" s="24"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="28" t="s">
-        <v>125</v>
+      <c r="A39" s="25" t="s">
+        <v>861</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="C39" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="D39" s="29">
-        <v>51</v>
-      </c>
-      <c r="E39" s="22">
-        <v>51</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C39" s="44"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
       <c r="F39" s="23" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="G39" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="I39" s="24">
-        <v>4.5</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="I39" s="24"/>
       <c r="J39" s="24"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="28" t="s">
-        <v>130</v>
+      <c r="A40" s="25" t="s">
+        <v>862</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="C40" s="44" t="s">
-        <v>132</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C40" s="44"/>
       <c r="D40" s="22"/>
       <c r="E40" s="22"/>
       <c r="F40" s="23" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G40" s="23" t="s">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="I40" s="24"/>
       <c r="J40" s="24"/>
     </row>
-    <row r="41" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="B41" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C41" s="47"/>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" s="44"/>
       <c r="D41" s="22"/>
       <c r="E41" s="22"/>
-      <c r="F41" s="29" t="s">
-        <v>703</v>
-      </c>
-      <c r="G41" s="23"/>
-      <c r="H41" s="7"/>
+      <c r="F41" s="23" t="s">
+        <v>697</v>
+      </c>
+      <c r="G41" s="23" t="s">
+        <v>47</v>
+      </c>
       <c r="I41" s="24"/>
       <c r="J41" s="24"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="B42" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" s="49"/>
+        <v>120</v>
+      </c>
+      <c r="B42" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42" s="44"/>
       <c r="D42" s="22"/>
       <c r="E42" s="22"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="4" t="s">
-        <v>137</v>
+      <c r="F42" s="23" t="s">
+        <v>700</v>
+      </c>
+      <c r="G42" s="23" t="s">
+        <v>122</v>
       </c>
       <c r="I42" s="24"/>
       <c r="J42" s="24"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="B43" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="C43" s="49"/>
+        <v>123</v>
+      </c>
+      <c r="B43" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="44"/>
       <c r="D43" s="22"/>
       <c r="E43" s="22"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
+      <c r="F43" s="23" t="s">
+        <v>701</v>
+      </c>
+      <c r="G43" s="23" t="s">
+        <v>122</v>
+      </c>
       <c r="I43" s="24"/>
       <c r="J43" s="24"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="B44" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" s="51"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="I44" s="24"/>
+      <c r="A44" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44" s="29">
+        <v>51</v>
+      </c>
+      <c r="E44" s="22">
+        <v>51</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>698</v>
+      </c>
+      <c r="G44" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="I44" s="24">
+        <v>4.5</v>
+      </c>
       <c r="J44" s="24"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B45" s="48" t="s">
-        <v>143</v>
-      </c>
-      <c r="C45" s="49" t="s">
-        <v>144</v>
+      <c r="A45" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" s="44" t="s">
+        <v>132</v>
       </c>
       <c r="D45" s="22"/>
       <c r="E45" s="22"/>
       <c r="F45" s="23" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="24"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="B46" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="C46" s="49" t="s">
-        <v>147</v>
+      <c r="A46" s="28" t="s">
+        <v>849</v>
+      </c>
+      <c r="B46" s="43" t="s">
+        <v>850</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>132</v>
       </c>
       <c r="D46" s="22"/>
       <c r="E46" s="22"/>
       <c r="F46" s="23" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="24"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="25" t="s">
-        <v>807</v>
-      </c>
-      <c r="B47" s="48" t="s">
-        <v>809</v>
-      </c>
-      <c r="C47" s="49"/>
+    <row r="47" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C47" s="47"/>
       <c r="D47" s="22"/>
       <c r="E47" s="22"/>
-      <c r="F47" s="23" t="s">
-        <v>808</v>
-      </c>
-      <c r="G47" s="23" t="s">
-        <v>129</v>
-      </c>
+      <c r="F47" s="29" t="s">
+        <v>702</v>
+      </c>
+      <c r="G47" s="23"/>
+      <c r="H47" s="7"/>
       <c r="I47" s="24"/>
       <c r="J47" s="24"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="25" t="s">
-        <v>810</v>
+        <v>135</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>809</v>
+        <v>136</v>
       </c>
       <c r="C48" s="49"/>
       <c r="D48" s="22"/>
       <c r="E48" s="22"/>
-      <c r="F48" s="23" t="s">
-        <v>811</v>
-      </c>
-      <c r="G48" s="23" t="s">
-        <v>24</v>
-      </c>
+      <c r="F48" s="23"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I48" s="24"/>
+      <c r="J48" s="24"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="C49" s="49" t="s">
-        <v>150</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C49" s="49"/>
       <c r="D49" s="22"/>
       <c r="E49" s="22"/>
-      <c r="F49" s="23" t="s">
-        <v>706</v>
-      </c>
-      <c r="G49" s="23" t="s">
-        <v>151</v>
-      </c>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
       <c r="I49" s="24"/>
       <c r="J49" s="24"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="B50" s="48" t="s">
-        <v>153</v>
-      </c>
-      <c r="C50" s="49"/>
+      <c r="A50" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C50" s="51"/>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
-      <c r="F50" s="23" t="s">
-        <v>788</v>
-      </c>
-      <c r="G50" s="23" t="s">
-        <v>151</v>
-      </c>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
       <c r="I50" s="24"/>
       <c r="J50" s="24"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="25" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>155</v>
-      </c>
-      <c r="C51" s="49"/>
+        <v>143</v>
+      </c>
+      <c r="C51" s="49" t="s">
+        <v>144</v>
+      </c>
       <c r="D51" s="22"/>
       <c r="E51" s="22"/>
       <c r="F51" s="23" t="s">
-        <v>789</v>
-      </c>
-      <c r="G51" s="23" t="s">
-        <v>29</v>
+        <v>703</v>
+      </c>
+      <c r="G51" s="191" t="s">
+        <v>15</v>
       </c>
       <c r="I51" s="24"/>
       <c r="J51" s="24"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="25" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B52" s="48" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="C52" s="49" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D52" s="22"/>
       <c r="E52" s="22"/>
       <c r="F52" s="23" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="I52" s="24"/>
       <c r="J52" s="24"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="25" t="s">
-        <v>159</v>
+        <v>804</v>
       </c>
       <c r="B53" s="48" t="s">
-        <v>160</v>
+        <v>806</v>
       </c>
       <c r="C53" s="49"/>
       <c r="D53" s="22"/>
       <c r="E53" s="22"/>
       <c r="F53" s="23" t="s">
-        <v>706</v>
-      </c>
-      <c r="G53" s="23" t="s">
-        <v>62</v>
+        <v>805</v>
+      </c>
+      <c r="G53" s="191" t="s">
+        <v>15</v>
       </c>
       <c r="I53" s="24"/>
       <c r="J53" s="24"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="B54" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="C54" s="53"/>
-      <c r="D54" s="22">
+        <v>807</v>
+      </c>
+      <c r="B54" s="48" t="s">
+        <v>806</v>
+      </c>
+      <c r="C54" s="49"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="23" t="s">
+        <v>808</v>
+      </c>
+      <c r="G54" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="E54" s="22">
-        <v>21</v>
-      </c>
-      <c r="F54" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="G54" s="23"/>
-      <c r="H54" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I54" s="24"/>
-      <c r="J54" s="24"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="B55" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="C55" s="55"/>
-      <c r="D55" s="22">
-        <v>21</v>
-      </c>
-      <c r="E55" s="22">
-        <v>15</v>
-      </c>
+      <c r="A55" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="B55" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
       <c r="F55" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="G55" s="23"/>
+        <v>705</v>
+      </c>
+      <c r="G55" s="23" t="s">
+        <v>151</v>
+      </c>
       <c r="I55" s="24"/>
       <c r="J55" s="24"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="25" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="B56" s="48" t="s">
-        <v>169</v>
-      </c>
-      <c r="C56" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="D56" s="22">
-        <v>30</v>
-      </c>
-      <c r="E56" s="22">
-        <v>24</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C56" s="49"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
       <c r="F56" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="G56" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>137</v>
+        <v>785</v>
+      </c>
+      <c r="G56" s="191" t="s">
+        <v>47</v>
       </c>
       <c r="I56" s="24"/>
       <c r="J56" s="24"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="25" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="B57" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="C57" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="D57" s="22">
-        <v>30</v>
-      </c>
-      <c r="E57" s="22">
-        <v>24</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C57" s="49"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
       <c r="F57" s="23" t="s">
-        <v>707</v>
-      </c>
-      <c r="G57" s="23" t="s">
-        <v>15</v>
+        <v>786</v>
+      </c>
+      <c r="G57" s="191" t="s">
+        <v>847</v>
       </c>
       <c r="I57" s="24"/>
       <c r="J57" s="24"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="25" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="B58" s="48" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="D58" s="22">
-        <v>30</v>
-      </c>
-      <c r="E58" s="22">
-        <v>24</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
       <c r="F58" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="G58" s="23" t="s">
-        <v>15</v>
+        <v>705</v>
+      </c>
+      <c r="G58" s="191" t="s">
+        <v>848</v>
       </c>
       <c r="I58" s="24"/>
       <c r="J58" s="24"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="25" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="C59" s="49"/>
-      <c r="D59" s="22">
-        <v>104</v>
-      </c>
-      <c r="E59" s="22">
-        <v>104</v>
-      </c>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
       <c r="F59" s="23" t="s">
-        <v>180</v>
+        <v>705</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="I59" s="24"/>
       <c r="J59" s="24"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="B60" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="C60" s="49"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
+        <v>161</v>
+      </c>
+      <c r="B60" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C60" s="53"/>
+      <c r="D60" s="22">
+        <v>24</v>
+      </c>
+      <c r="E60" s="22">
+        <v>21</v>
+      </c>
       <c r="F60" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="G60" s="23" t="s">
-        <v>47</v>
+        <v>163</v>
+      </c>
+      <c r="G60" s="23"/>
+      <c r="H60" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="I60" s="24"/>
       <c r="J60" s="24"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="B61" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="C61" s="49"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
+      <c r="A61" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="B61" s="54" t="s">
+        <v>166</v>
+      </c>
+      <c r="C61" s="55"/>
+      <c r="D61" s="22">
+        <v>21</v>
+      </c>
+      <c r="E61" s="22">
+        <v>15</v>
+      </c>
       <c r="F61" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="G61" s="23" t="s">
-        <v>29</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="G61" s="23"/>
       <c r="I61" s="24"/>
       <c r="J61" s="24"/>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="25" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="B62" s="48" t="s">
-        <v>186</v>
-      </c>
-      <c r="C62" s="49"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
+        <v>169</v>
+      </c>
+      <c r="C62" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="D62" s="22">
+        <v>30</v>
+      </c>
+      <c r="E62" s="22">
+        <v>24</v>
+      </c>
+      <c r="F62" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="G62" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="I62" s="24"/>
       <c r="J62" s="24"/>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="25" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B63" s="48" t="s">
-        <v>188</v>
-      </c>
-      <c r="C63" s="49"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
+        <v>173</v>
+      </c>
+      <c r="C63" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="D63" s="22">
+        <v>30</v>
+      </c>
+      <c r="E63" s="22">
+        <v>24</v>
+      </c>
+      <c r="F63" s="23" t="s">
+        <v>706</v>
+      </c>
+      <c r="G63" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="I63" s="24"/>
       <c r="J63" s="24"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="25" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B64" s="48" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C64" s="49" t="s">
         <v>170</v>
@@ -5371,7 +5618,7 @@
         <v>24</v>
       </c>
       <c r="F64" s="23" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="G64" s="23" t="s">
         <v>15</v>
@@ -5379,194 +5626,189 @@
       <c r="I64" s="24"/>
       <c r="J64" s="24"/>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="25" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B65" s="48" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="C65" s="49"/>
       <c r="D65" s="22">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="E65" s="22">
-        <v>24</v>
-      </c>
-      <c r="F65" s="23"/>
-      <c r="G65" s="23"/>
+        <v>104</v>
+      </c>
+      <c r="F65" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="G65" s="23" t="s">
+        <v>47</v>
+      </c>
       <c r="I65" s="24"/>
       <c r="J65" s="24"/>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="25" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B66" s="48" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="C66" s="49"/>
-      <c r="D66" s="22">
-        <v>104</v>
-      </c>
-      <c r="E66" s="22">
-        <v>104</v>
-      </c>
-      <c r="F66" s="23"/>
-      <c r="G66" s="23"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="G66" s="23" t="s">
+        <v>47</v>
+      </c>
       <c r="I66" s="24"/>
       <c r="J66" s="24"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="25" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="B67" s="48" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="C67" s="49"/>
       <c r="D67" s="22"/>
       <c r="E67" s="22"/>
       <c r="F67" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="G67" s="23"/>
+        <v>184</v>
+      </c>
+      <c r="G67" s="191" t="s">
+        <v>847</v>
+      </c>
       <c r="I67" s="24"/>
       <c r="J67" s="24"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="25" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B68" s="48" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="C68" s="49"/>
       <c r="D68" s="22"/>
       <c r="E68" s="22"/>
-      <c r="F68" s="23" t="s">
-        <v>201</v>
-      </c>
+      <c r="F68" s="23"/>
       <c r="G68" s="23"/>
       <c r="I68" s="24"/>
       <c r="J68" s="24"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="25" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B69" s="48" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C69" s="49"/>
       <c r="D69" s="22"/>
       <c r="E69" s="22"/>
-      <c r="F69" s="23" t="s">
-        <v>204</v>
-      </c>
+      <c r="F69" s="23"/>
       <c r="G69" s="23"/>
       <c r="I69" s="24"/>
       <c r="J69" s="24"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="25" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="B70" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="C70" s="49"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
+        <v>190</v>
+      </c>
+      <c r="C70" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="D70" s="22">
+        <v>30</v>
+      </c>
+      <c r="E70" s="22">
+        <v>24</v>
+      </c>
       <c r="F70" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="G70" s="23"/>
+        <v>191</v>
+      </c>
+      <c r="G70" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="I70" s="24"/>
       <c r="J70" s="24"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="B71" s="50" t="s">
-        <v>209</v>
-      </c>
-      <c r="C71" s="51"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="23" t="s">
-        <v>210</v>
-      </c>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="B71" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="C71" s="49"/>
+      <c r="D71" s="22">
+        <v>30</v>
+      </c>
+      <c r="E71" s="22">
+        <v>24</v>
+      </c>
+      <c r="F71" s="23"/>
       <c r="G71" s="23"/>
       <c r="I71" s="24"/>
       <c r="J71" s="24"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="B72" s="56" t="s">
-        <v>212</v>
-      </c>
-      <c r="C72" s="34" t="s">
-        <v>60</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="B72" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="C72" s="49"/>
       <c r="D72" s="22">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="E72" s="22">
-        <v>20</v>
-      </c>
-      <c r="F72" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="G72" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>214</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="F72" s="23"/>
+      <c r="G72" s="23"/>
       <c r="I72" s="24"/>
       <c r="J72" s="24"/>
     </row>
     <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="B73" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="C73" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="D73" s="22">
-        <v>24</v>
-      </c>
-      <c r="E73" s="22">
-        <v>18</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="B73" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="C73" s="49"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
       <c r="F73" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="G73" s="23" t="s">
-        <v>29</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G73" s="23"/>
       <c r="I73" s="24"/>
       <c r="J73" s="24"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="B74" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="C74" s="57"/>
+        <v>199</v>
+      </c>
+      <c r="B74" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="C74" s="49"/>
       <c r="D74" s="22"/>
       <c r="E74" s="22"/>
       <c r="F74" s="23" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="G74" s="23"/>
       <c r="I74" s="24"/>
@@ -5574,99 +5816,101 @@
     </row>
     <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="B75" s="56" t="s">
-        <v>222</v>
-      </c>
-      <c r="C75" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="D75" s="22">
-        <v>24</v>
-      </c>
-      <c r="E75" s="22">
-        <v>18</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="B75" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="C75" s="49"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
       <c r="F75" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="G75" s="23" t="s">
-        <v>29</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G75" s="23"/>
       <c r="I75" s="24"/>
       <c r="J75" s="24"/>
     </row>
-    <row r="76" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="B76" s="56" t="s">
-        <v>225</v>
-      </c>
-      <c r="C76" s="34"/>
+        <v>205</v>
+      </c>
+      <c r="B76" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="C76" s="49"/>
       <c r="D76" s="22"/>
       <c r="E76" s="22"/>
-      <c r="F76" s="29" t="s">
-        <v>708</v>
+      <c r="F76" s="23" t="s">
+        <v>207</v>
       </c>
       <c r="G76" s="23"/>
-      <c r="H76" s="7"/>
       <c r="I76" s="24"/>
       <c r="J76" s="24"/>
     </row>
     <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="B77" s="56" t="s">
-        <v>227</v>
-      </c>
-      <c r="C77" s="57"/>
+      <c r="A77" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="B77" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="C77" s="51"/>
       <c r="D77" s="22"/>
       <c r="E77" s="22"/>
       <c r="F77" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="G77" s="23" t="s">
-        <v>29</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="G77" s="23"/>
       <c r="I77" s="24"/>
       <c r="J77" s="24"/>
     </row>
-    <row r="78" spans="1:10" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="25" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="B78" s="56" t="s">
-        <v>230</v>
-      </c>
-      <c r="C78" s="57"/>
-      <c r="D78" s="22"/>
-      <c r="E78" s="22"/>
+        <v>212</v>
+      </c>
+      <c r="C78" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D78" s="22">
+        <v>30</v>
+      </c>
+      <c r="E78" s="22">
+        <v>20</v>
+      </c>
       <c r="F78" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="G78" s="23"/>
+        <v>213</v>
+      </c>
+      <c r="G78" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="I78" s="24"/>
       <c r="J78" s="24"/>
     </row>
     <row r="79" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="25" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="B79" s="56" t="s">
-        <v>233</v>
-      </c>
-      <c r="C79" s="57"/>
+        <v>216</v>
+      </c>
+      <c r="C79" s="34" t="s">
+        <v>66</v>
+      </c>
       <c r="D79" s="22">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E79" s="22">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="G79" s="23" t="s">
         <v>29</v>
@@ -5674,345 +5918,332 @@
       <c r="I79" s="24"/>
       <c r="J79" s="24"/>
     </row>
-    <row r="80" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="25" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="B80" s="56" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="C80" s="57"/>
       <c r="D80" s="22"/>
       <c r="E80" s="22"/>
       <c r="F80" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="G80" s="23" t="s">
-        <v>29</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G80" s="23"/>
       <c r="I80" s="24"/>
       <c r="J80" s="24"/>
     </row>
     <row r="81" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="25" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="B81" s="56" t="s">
-        <v>239</v>
-      </c>
-      <c r="C81" s="57"/>
+        <v>222</v>
+      </c>
+      <c r="C81" s="34" t="s">
+        <v>66</v>
+      </c>
       <c r="D81" s="22">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E81" s="22">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="G81" s="23" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="I81" s="24"/>
       <c r="J81" s="24"/>
     </row>
-    <row r="82" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="B82" s="58" t="s">
-        <v>242</v>
-      </c>
-      <c r="C82" s="59" t="s">
-        <v>243</v>
-      </c>
-      <c r="D82" s="22">
-        <v>36</v>
-      </c>
-      <c r="E82" s="22">
-        <v>30</v>
-      </c>
-      <c r="F82" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="G82" s="23" t="s">
-        <v>15</v>
-      </c>
+    <row r="82" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="B82" s="56" t="s">
+        <v>225</v>
+      </c>
+      <c r="C82" s="34"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="29" t="s">
+        <v>707</v>
+      </c>
+      <c r="G82" s="23"/>
+      <c r="H82" s="7"/>
       <c r="I82" s="24"/>
       <c r="J82" s="24"/>
     </row>
     <row r="83" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="30" t="s">
-        <v>795</v>
-      </c>
-      <c r="B83" s="58" t="s">
-        <v>796</v>
-      </c>
-      <c r="C83" s="59"/>
+      <c r="A83" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="B83" s="56" t="s">
+        <v>227</v>
+      </c>
+      <c r="C83" s="57"/>
       <c r="D83" s="22"/>
       <c r="E83" s="22"/>
-      <c r="F83" s="23"/>
+      <c r="F83" s="23" t="s">
+        <v>228</v>
+      </c>
       <c r="G83" s="23" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="I83" s="24"/>
       <c r="J83" s="24"/>
     </row>
-    <row r="84" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="B84" s="58" t="s">
-        <v>246</v>
-      </c>
-      <c r="C84" s="59"/>
+    <row r="84" spans="1:10" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="B84" s="56" t="s">
+        <v>230</v>
+      </c>
+      <c r="C84" s="57"/>
       <c r="D84" s="22"/>
       <c r="E84" s="22"/>
       <c r="F84" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="G84" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H84" s="7"/>
+        <v>231</v>
+      </c>
+      <c r="G84" s="23"/>
       <c r="I84" s="24"/>
       <c r="J84" s="24"/>
     </row>
-    <row r="85" spans="1:10" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="60"/>
-      <c r="B85" s="61"/>
-      <c r="C85" s="62"/>
-      <c r="F85" s="61"/>
-      <c r="G85" s="61"/>
-      <c r="H85" s="63"/>
+    <row r="85" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="B85" s="56" t="s">
+        <v>233</v>
+      </c>
+      <c r="C85" s="57"/>
+      <c r="D85" s="22">
+        <v>27</v>
+      </c>
+      <c r="E85" s="22">
+        <v>21</v>
+      </c>
+      <c r="F85" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="G85" s="23" t="s">
+        <v>29</v>
+      </c>
       <c r="I85" s="24"/>
       <c r="J85" s="24"/>
     </row>
-    <row r="86" spans="1:10" s="11" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="192" t="s">
-        <v>248</v>
-      </c>
-      <c r="B86" s="192"/>
-      <c r="C86" s="192"/>
-      <c r="D86" s="192"/>
-      <c r="E86" s="192"/>
-      <c r="F86" s="192"/>
-      <c r="G86" s="64"/>
-      <c r="H86" s="65"/>
+    <row r="86" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="B86" s="56" t="s">
+        <v>236</v>
+      </c>
+      <c r="C86" s="57"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="G86" s="23" t="s">
+        <v>29</v>
+      </c>
       <c r="I86" s="24"/>
       <c r="J86" s="24"/>
     </row>
-    <row r="87" spans="1:10" s="69" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="B87" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="C87" s="15"/>
-      <c r="D87" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="E87" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="G87" s="15"/>
-      <c r="H87" s="67"/>
-      <c r="I87" s="68"/>
-      <c r="J87" s="68"/>
-    </row>
-    <row r="88" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="70" t="s">
-        <v>252</v>
-      </c>
-      <c r="B88" s="71" t="s">
-        <v>253</v>
-      </c>
-      <c r="C88" s="71"/>
-      <c r="D88" s="72"/>
-      <c r="E88" s="72"/>
-      <c r="F88" s="73" t="s">
-        <v>709</v>
-      </c>
-      <c r="G88" s="73" t="s">
+    <row r="87" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="B87" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="C87" s="57"/>
+      <c r="D87" s="22">
+        <v>30</v>
+      </c>
+      <c r="E87" s="22">
+        <v>30</v>
+      </c>
+      <c r="F87" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="G87" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="H88" s="2" t="s">
-        <v>214</v>
+      <c r="I87" s="24"/>
+      <c r="J87" s="24"/>
+    </row>
+    <row r="88" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="B88" s="58" t="s">
+        <v>242</v>
+      </c>
+      <c r="C88" s="59" t="s">
+        <v>170</v>
+      </c>
+      <c r="D88" s="22">
+        <v>36</v>
+      </c>
+      <c r="E88" s="22">
+        <v>30</v>
+      </c>
+      <c r="F88" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="G88" s="23" t="s">
+        <v>15</v>
       </c>
       <c r="I88" s="24"/>
       <c r="J88" s="24"/>
     </row>
-    <row r="89" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="B89" s="74" t="s">
-        <v>256</v>
-      </c>
-      <c r="C89" s="75"/>
+        <v>792</v>
+      </c>
+      <c r="B89" s="58" t="s">
+        <v>793</v>
+      </c>
+      <c r="C89" s="59"/>
       <c r="D89" s="22"/>
       <c r="E89" s="22"/>
-      <c r="F89" s="73" t="s">
-        <v>257</v>
-      </c>
-      <c r="G89" s="76" t="s">
-        <v>47</v>
-      </c>
-      <c r="H89" s="77" t="s">
-        <v>258</v>
-      </c>
+      <c r="F89" s="23"/>
+      <c r="G89" s="23"/>
       <c r="I89" s="24"/>
       <c r="J89" s="24"/>
     </row>
     <row r="90" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="B90" s="78" t="s">
-        <v>260</v>
-      </c>
-      <c r="C90" s="79"/>
+      <c r="A90" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="B90" s="58" t="s">
+        <v>245</v>
+      </c>
+      <c r="C90" s="59"/>
       <c r="D90" s="22"/>
       <c r="E90" s="22"/>
       <c r="F90" s="23" t="s">
-        <v>710</v>
+        <v>246</v>
       </c>
       <c r="G90" s="23" t="s">
-        <v>261</v>
+        <v>15</v>
       </c>
       <c r="H90" s="7"/>
       <c r="I90" s="24"/>
       <c r="J90" s="24"/>
     </row>
-    <row r="91" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="B91" s="78" t="s">
-        <v>263</v>
-      </c>
-      <c r="C91" s="79"/>
-      <c r="D91" s="22"/>
-      <c r="E91" s="22"/>
-      <c r="F91" s="23" t="s">
-        <v>711</v>
-      </c>
-      <c r="G91" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="H91" s="7"/>
+    <row r="91" spans="1:10" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="60"/>
+      <c r="B91" s="61"/>
+      <c r="C91" s="62"/>
+      <c r="F91" s="61"/>
+      <c r="G91" s="61"/>
+      <c r="H91" s="63"/>
       <c r="I91" s="24"/>
       <c r="J91" s="24"/>
     </row>
-    <row r="92" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="B92" s="78" t="s">
-        <v>265</v>
-      </c>
-      <c r="C92" s="79" t="s">
-        <v>80</v>
-      </c>
-      <c r="D92" s="22"/>
-      <c r="E92" s="22"/>
-      <c r="F92" s="73" t="s">
-        <v>736</v>
-      </c>
-      <c r="G92" s="80" t="s">
-        <v>129</v>
-      </c>
-      <c r="H92" s="7"/>
+    <row r="92" spans="1:10" s="11" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="217" t="s">
+        <v>247</v>
+      </c>
+      <c r="B92" s="217"/>
+      <c r="C92" s="217"/>
+      <c r="D92" s="217"/>
+      <c r="E92" s="217"/>
+      <c r="F92" s="217"/>
+      <c r="G92" s="64"/>
+      <c r="H92" s="65"/>
       <c r="I92" s="24"/>
       <c r="J92" s="24"/>
     </row>
-    <row r="93" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="B93" s="78" t="s">
-        <v>267</v>
-      </c>
-      <c r="C93" s="79" t="s">
-        <v>80</v>
-      </c>
-      <c r="D93" s="22"/>
-      <c r="E93" s="22"/>
-      <c r="F93" s="80" t="s">
-        <v>737</v>
-      </c>
-      <c r="G93" s="80" t="s">
+    <row r="93" spans="1:10" s="69" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C93" s="15"/>
+      <c r="D93" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="E93" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="G93" s="15"/>
+      <c r="H93" s="67"/>
+      <c r="I93" s="68"/>
+      <c r="J93" s="68"/>
+    </row>
+    <row r="94" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="70" t="s">
+        <v>251</v>
+      </c>
+      <c r="B94" s="71" t="s">
+        <v>252</v>
+      </c>
+      <c r="C94" s="71"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="72"/>
+      <c r="F94" s="73" t="s">
+        <v>708</v>
+      </c>
+      <c r="G94" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="H93" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="I93" s="24"/>
-      <c r="J93" s="24"/>
-    </row>
-    <row r="94" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="25" t="s">
-        <v>270</v>
-      </c>
-      <c r="B94" s="81" t="s">
-        <v>271</v>
-      </c>
-      <c r="C94" s="82"/>
-      <c r="D94" s="22"/>
-      <c r="E94" s="22"/>
-      <c r="F94" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="G94" s="80" t="s">
-        <v>129</v>
-      </c>
-      <c r="H94" s="83" t="s">
-        <v>273</v>
+      <c r="H94" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="I94" s="24"/>
       <c r="J94" s="24"/>
     </row>
     <row r="95" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="25" t="s">
-        <v>274</v>
-      </c>
-      <c r="B95" s="78" t="s">
-        <v>275</v>
-      </c>
-      <c r="C95" s="79" t="s">
-        <v>80</v>
-      </c>
+      <c r="A95" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B95" s="74" t="s">
+        <v>255</v>
+      </c>
+      <c r="C95" s="75"/>
       <c r="D95" s="22"/>
       <c r="E95" s="22"/>
-      <c r="F95" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="G95" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="H95" s="7"/>
+      <c r="F95" s="73" t="s">
+        <v>256</v>
+      </c>
+      <c r="G95" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="H95" s="77" t="s">
+        <v>257</v>
+      </c>
       <c r="I95" s="24"/>
       <c r="J95" s="24"/>
     </row>
     <row r="96" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="25" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="B96" s="78" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="C96" s="79"/>
       <c r="D96" s="22"/>
       <c r="E96" s="22"/>
-      <c r="F96" s="73" t="s">
-        <v>787</v>
+      <c r="F96" s="23" t="s">
+        <v>709</v>
       </c>
       <c r="G96" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H96" s="7"/>
       <c r="I96" s="24"/>
@@ -6020,19 +6251,19 @@
     </row>
     <row r="97" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="25" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="B97" s="78" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="C97" s="79"/>
       <c r="D97" s="22"/>
       <c r="E97" s="22"/>
-      <c r="F97" s="73" t="s">
-        <v>786</v>
+      <c r="F97" s="23" t="s">
+        <v>710</v>
       </c>
       <c r="G97" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H97" s="7"/>
       <c r="I97" s="24"/>
@@ -6040,19 +6271,21 @@
     </row>
     <row r="98" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="25" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="B98" s="78" t="s">
-        <v>282</v>
-      </c>
-      <c r="C98" s="79"/>
+        <v>264</v>
+      </c>
+      <c r="C98" s="79" t="s">
+        <v>80</v>
+      </c>
       <c r="D98" s="22"/>
       <c r="E98" s="22"/>
       <c r="F98" s="73" t="s">
-        <v>785</v>
-      </c>
-      <c r="G98" s="23" t="s">
-        <v>261</v>
+        <v>733</v>
+      </c>
+      <c r="G98" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H98" s="7"/>
       <c r="I98" s="24"/>
@@ -6060,57 +6293,67 @@
     </row>
     <row r="99" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="25" t="s">
-        <v>801</v>
+        <v>265</v>
       </c>
       <c r="B99" s="78" t="s">
-        <v>802</v>
-      </c>
-      <c r="C99" s="79"/>
+        <v>266</v>
+      </c>
+      <c r="C99" s="79" t="s">
+        <v>80</v>
+      </c>
       <c r="D99" s="22"/>
       <c r="E99" s="22"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="H99" s="7"/>
+      <c r="F99" s="80" t="s">
+        <v>734</v>
+      </c>
+      <c r="G99" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="I99" s="24"/>
       <c r="J99" s="24"/>
     </row>
     <row r="100" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="25" t="s">
-        <v>283</v>
-      </c>
-      <c r="B100" s="78" t="s">
-        <v>284</v>
-      </c>
-      <c r="C100" s="79"/>
+        <v>269</v>
+      </c>
+      <c r="B100" s="81" t="s">
+        <v>270</v>
+      </c>
+      <c r="C100" s="82"/>
       <c r="D100" s="22"/>
       <c r="E100" s="22"/>
       <c r="F100" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="G100" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="H100" s="7"/>
+        <v>271</v>
+      </c>
+      <c r="G100" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="H100" s="83" t="s">
+        <v>272</v>
+      </c>
       <c r="I100" s="24"/>
       <c r="J100" s="24"/>
     </row>
     <row r="101" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="25" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B101" s="78" t="s">
-        <v>287</v>
-      </c>
-      <c r="C101" s="79"/>
+        <v>274</v>
+      </c>
+      <c r="C101" s="79" t="s">
+        <v>80</v>
+      </c>
       <c r="D101" s="22"/>
       <c r="E101" s="22"/>
-      <c r="F101" s="73" t="s">
-        <v>784</v>
+      <c r="F101" s="29" t="s">
+        <v>275</v>
       </c>
       <c r="G101" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H101" s="7"/>
       <c r="I101" s="24"/>
@@ -6118,19 +6361,19 @@
     </row>
     <row r="102" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="25" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B102" s="78" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="C102" s="79"/>
       <c r="D102" s="22"/>
       <c r="E102" s="22"/>
       <c r="F102" s="73" t="s">
-        <v>712</v>
+        <v>784</v>
       </c>
       <c r="G102" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H102" s="7"/>
       <c r="I102" s="24"/>
@@ -6138,19 +6381,19 @@
     </row>
     <row r="103" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="25" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="B103" s="78" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="C103" s="79"/>
       <c r="D103" s="22"/>
       <c r="E103" s="22"/>
       <c r="F103" s="73" t="s">
-        <v>710</v>
+        <v>783</v>
       </c>
       <c r="G103" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H103" s="7"/>
       <c r="I103" s="24"/>
@@ -6158,19 +6401,19 @@
     </row>
     <row r="104" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="25" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B104" s="78" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C104" s="79"/>
       <c r="D104" s="22"/>
       <c r="E104" s="22"/>
       <c r="F104" s="73" t="s">
-        <v>713</v>
+        <v>782</v>
       </c>
       <c r="G104" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H104" s="7"/>
       <c r="I104" s="24"/>
@@ -6178,19 +6421,17 @@
     </row>
     <row r="105" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="25" t="s">
-        <v>293</v>
+        <v>798</v>
       </c>
       <c r="B105" s="78" t="s">
-        <v>294</v>
+        <v>799</v>
       </c>
       <c r="C105" s="79"/>
       <c r="D105" s="22"/>
       <c r="E105" s="22"/>
-      <c r="F105" s="80" t="s">
-        <v>295</v>
-      </c>
-      <c r="G105" s="80" t="s">
-        <v>261</v>
+      <c r="F105" s="73"/>
+      <c r="G105" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H105" s="7"/>
       <c r="I105" s="24"/>
@@ -6198,19 +6439,19 @@
     </row>
     <row r="106" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="25" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="B106" s="78" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="C106" s="79"/>
       <c r="D106" s="22"/>
       <c r="E106" s="22"/>
-      <c r="F106" s="73" t="s">
-        <v>782</v>
+      <c r="F106" s="29" t="s">
+        <v>284</v>
       </c>
       <c r="G106" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H106" s="7"/>
       <c r="I106" s="24"/>
@@ -6218,19 +6459,19 @@
     </row>
     <row r="107" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="25" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="B107" s="78" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="C107" s="79"/>
       <c r="D107" s="22"/>
       <c r="E107" s="22"/>
       <c r="F107" s="73" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G107" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H107" s="7"/>
       <c r="I107" s="24"/>
@@ -6238,19 +6479,19 @@
     </row>
     <row r="108" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="25" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="B108" s="78" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="C108" s="79"/>
       <c r="D108" s="22"/>
       <c r="E108" s="22"/>
       <c r="F108" s="73" t="s">
-        <v>738</v>
-      </c>
-      <c r="G108" s="80" t="s">
-        <v>129</v>
+        <v>711</v>
+      </c>
+      <c r="G108" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H108" s="7"/>
       <c r="I108" s="24"/>
@@ -6258,19 +6499,19 @@
     </row>
     <row r="109" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="25" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="B109" s="78" t="s">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="C109" s="79"/>
       <c r="D109" s="22"/>
       <c r="E109" s="22"/>
       <c r="F109" s="73" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="G109" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H109" s="7"/>
       <c r="I109" s="24"/>
@@ -6278,19 +6519,19 @@
     </row>
     <row r="110" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="25" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B110" s="78" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C110" s="79"/>
       <c r="D110" s="22"/>
       <c r="E110" s="22"/>
       <c r="F110" s="73" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="G110" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H110" s="7"/>
       <c r="I110" s="24"/>
@@ -6298,39 +6539,39 @@
     </row>
     <row r="111" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="25" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="B111" s="78" t="s">
-        <v>307</v>
-      </c>
-      <c r="C111" s="79" t="s">
-        <v>80</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="C111" s="79"/>
       <c r="D111" s="22"/>
       <c r="E111" s="22"/>
-      <c r="F111" s="73" t="s">
-        <v>739</v>
-      </c>
-      <c r="G111" s="23" t="s">
-        <v>261</v>
+      <c r="F111" s="80" t="s">
+        <v>294</v>
+      </c>
+      <c r="G111" s="80" t="s">
+        <v>260</v>
       </c>
       <c r="H111" s="7"/>
       <c r="I111" s="24"/>
       <c r="J111" s="24"/>
     </row>
-    <row r="112" spans="1:10" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="B112" s="78"/>
+        <v>295</v>
+      </c>
+      <c r="B112" s="78" t="s">
+        <v>296</v>
+      </c>
       <c r="C112" s="79"/>
       <c r="D112" s="22"/>
       <c r="E112" s="22"/>
-      <c r="F112" s="80" t="s">
-        <v>309</v>
-      </c>
-      <c r="G112" s="80" t="s">
-        <v>129</v>
+      <c r="F112" s="73" t="s">
+        <v>779</v>
+      </c>
+      <c r="G112" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H112" s="7"/>
       <c r="I112" s="24"/>
@@ -6338,19 +6579,19 @@
     </row>
     <row r="113" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="25" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="B113" s="78" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="C113" s="79"/>
       <c r="D113" s="22"/>
       <c r="E113" s="22"/>
       <c r="F113" s="73" t="s">
-        <v>716</v>
+        <v>780</v>
       </c>
       <c r="G113" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H113" s="7"/>
       <c r="I113" s="24"/>
@@ -6358,19 +6599,19 @@
     </row>
     <row r="114" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="25" t="s">
-        <v>815</v>
+        <v>299</v>
       </c>
       <c r="B114" s="78" t="s">
-        <v>818</v>
+        <v>300</v>
       </c>
       <c r="C114" s="79"/>
       <c r="D114" s="22"/>
       <c r="E114" s="22"/>
       <c r="F114" s="73" t="s">
-        <v>819</v>
-      </c>
-      <c r="G114" s="23" t="s">
-        <v>261</v>
+        <v>735</v>
+      </c>
+      <c r="G114" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H114" s="7"/>
       <c r="I114" s="24"/>
@@ -6378,19 +6619,19 @@
     </row>
     <row r="115" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="25" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="B115" s="78" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="C115" s="79"/>
       <c r="D115" s="22"/>
       <c r="E115" s="22"/>
       <c r="F115" s="73" t="s">
-        <v>747</v>
+        <v>713</v>
       </c>
       <c r="G115" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H115" s="7"/>
       <c r="I115" s="24"/>
@@ -6398,19 +6639,19 @@
     </row>
     <row r="116" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="25" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="B116" s="78" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="C116" s="79"/>
       <c r="D116" s="22"/>
       <c r="E116" s="22"/>
       <c r="F116" s="73" t="s">
-        <v>748</v>
+        <v>714</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H116" s="7"/>
       <c r="I116" s="24"/>
@@ -6418,39 +6659,39 @@
     </row>
     <row r="117" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="25" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="B117" s="78" t="s">
-        <v>317</v>
-      </c>
-      <c r="C117" s="79"/>
+        <v>306</v>
+      </c>
+      <c r="C117" s="79" t="s">
+        <v>80</v>
+      </c>
       <c r="D117" s="22"/>
       <c r="E117" s="22"/>
       <c r="F117" s="73" t="s">
-        <v>781</v>
+        <v>736</v>
       </c>
       <c r="G117" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H117" s="7"/>
       <c r="I117" s="24"/>
       <c r="J117" s="24"/>
     </row>
-    <row r="118" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="25" t="s">
-        <v>318</v>
-      </c>
-      <c r="B118" s="78" t="s">
-        <v>319</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="B118" s="78"/>
       <c r="C118" s="79"/>
       <c r="D118" s="22"/>
       <c r="E118" s="22"/>
-      <c r="F118" s="73" t="s">
-        <v>717</v>
-      </c>
-      <c r="G118" s="23" t="s">
-        <v>261</v>
+      <c r="F118" s="80" t="s">
+        <v>308</v>
+      </c>
+      <c r="G118" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H118" s="7"/>
       <c r="I118" s="24"/>
@@ -6458,19 +6699,19 @@
     </row>
     <row r="119" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="25" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="B119" s="78" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="C119" s="79"/>
       <c r="D119" s="22"/>
       <c r="E119" s="22"/>
       <c r="F119" s="73" t="s">
-        <v>749</v>
+        <v>715</v>
       </c>
       <c r="G119" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H119" s="7"/>
       <c r="I119" s="24"/>
@@ -6478,19 +6719,19 @@
     </row>
     <row r="120" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="25" t="s">
-        <v>322</v>
+        <v>812</v>
       </c>
       <c r="B120" s="78" t="s">
-        <v>323</v>
+        <v>815</v>
       </c>
       <c r="C120" s="79"/>
       <c r="D120" s="22"/>
       <c r="E120" s="22"/>
       <c r="F120" s="73" t="s">
-        <v>750</v>
+        <v>816</v>
       </c>
       <c r="G120" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H120" s="7"/>
       <c r="I120" s="24"/>
@@ -6498,19 +6739,19 @@
     </row>
     <row r="121" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="25" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="B121" s="78" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="C121" s="79"/>
       <c r="D121" s="22"/>
       <c r="E121" s="22"/>
       <c r="F121" s="73" t="s">
-        <v>718</v>
+        <v>744</v>
       </c>
       <c r="G121" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H121" s="7"/>
       <c r="I121" s="24"/>
@@ -6518,19 +6759,19 @@
     </row>
     <row r="122" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="25" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="B122" s="78" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="C122" s="79"/>
       <c r="D122" s="22"/>
       <c r="E122" s="22"/>
       <c r="F122" s="73" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="G122" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H122" s="7"/>
       <c r="I122" s="24"/>
@@ -6538,19 +6779,19 @@
     </row>
     <row r="123" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="25" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="B123" s="78" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="C123" s="79"/>
       <c r="D123" s="22"/>
       <c r="E123" s="22"/>
       <c r="F123" s="73" t="s">
-        <v>719</v>
+        <v>778</v>
       </c>
       <c r="G123" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H123" s="7"/>
       <c r="I123" s="24"/>
@@ -6558,19 +6799,19 @@
     </row>
     <row r="124" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="25" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="B124" s="78" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="C124" s="79"/>
       <c r="D124" s="22"/>
       <c r="E124" s="22"/>
-      <c r="F124" s="29" t="s">
-        <v>332</v>
-      </c>
-      <c r="G124" s="80" t="s">
-        <v>129</v>
+      <c r="F124" s="73" t="s">
+        <v>854</v>
+      </c>
+      <c r="G124" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H124" s="7"/>
       <c r="I124" s="24"/>
@@ -6578,19 +6819,19 @@
     </row>
     <row r="125" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="25" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="B125" s="78" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="C125" s="79"/>
       <c r="D125" s="22"/>
       <c r="E125" s="22"/>
-      <c r="F125" s="80" t="s">
-        <v>780</v>
-      </c>
-      <c r="G125" s="80" t="s">
-        <v>129</v>
+      <c r="F125" s="73" t="s">
+        <v>746</v>
+      </c>
+      <c r="G125" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H125" s="7"/>
       <c r="I125" s="24"/>
@@ -6598,39 +6839,39 @@
     </row>
     <row r="126" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="25" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="B126" s="78" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="C126" s="79"/>
       <c r="D126" s="22"/>
       <c r="E126" s="22"/>
-      <c r="F126" s="80" t="s">
-        <v>752</v>
-      </c>
-      <c r="G126" s="80" t="s">
-        <v>129</v>
+      <c r="F126" s="73" t="s">
+        <v>747</v>
+      </c>
+      <c r="G126" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H126" s="7"/>
-      <c r="I126" s="84"/>
-      <c r="J126" s="84"/>
+      <c r="I126" s="24"/>
+      <c r="J126" s="24"/>
     </row>
     <row r="127" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="25" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="B127" s="78" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="C127" s="79"/>
       <c r="D127" s="22"/>
       <c r="E127" s="22"/>
       <c r="F127" s="73" t="s">
-        <v>753</v>
-      </c>
-      <c r="G127" s="80" t="s">
-        <v>129</v>
+        <v>716</v>
+      </c>
+      <c r="G127" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H127" s="7"/>
       <c r="I127" s="24"/>
@@ -6638,99 +6879,99 @@
     </row>
     <row r="128" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="25" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="B128" s="78" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="C128" s="79"/>
       <c r="D128" s="22"/>
       <c r="E128" s="22"/>
-      <c r="F128" s="80" t="s">
-        <v>343</v>
-      </c>
-      <c r="G128" s="73" t="s">
-        <v>261</v>
+      <c r="F128" s="73" t="s">
+        <v>748</v>
+      </c>
+      <c r="G128" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H128" s="7"/>
-      <c r="I128" s="84"/>
-      <c r="J128" s="84"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="24"/>
     </row>
     <row r="129" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="25" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="B129" s="78" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="C129" s="79"/>
       <c r="D129" s="22"/>
       <c r="E129" s="22"/>
-      <c r="F129" s="80" t="s">
-        <v>346</v>
-      </c>
-      <c r="G129" s="80" t="s">
-        <v>261</v>
+      <c r="F129" s="73" t="s">
+        <v>717</v>
+      </c>
+      <c r="G129" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H129" s="7"/>
-      <c r="I129" s="84"/>
-      <c r="J129" s="84"/>
+      <c r="I129" s="24"/>
+      <c r="J129" s="24"/>
     </row>
     <row r="130" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="25" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="B130" s="78" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="C130" s="79"/>
       <c r="D130" s="22"/>
       <c r="E130" s="22"/>
-      <c r="F130" s="80" t="s">
-        <v>754</v>
+      <c r="F130" s="29" t="s">
+        <v>331</v>
       </c>
       <c r="G130" s="80" t="s">
         <v>129</v>
       </c>
       <c r="H130" s="7"/>
-      <c r="I130" s="84"/>
-      <c r="J130" s="84"/>
+      <c r="I130" s="24"/>
+      <c r="J130" s="24"/>
     </row>
     <row r="131" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="25" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="B131" s="78" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="C131" s="79"/>
       <c r="D131" s="22"/>
       <c r="E131" s="22"/>
       <c r="F131" s="80" t="s">
-        <v>755</v>
-      </c>
-      <c r="G131" s="73" t="s">
-        <v>261</v>
+        <v>777</v>
+      </c>
+      <c r="G131" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H131" s="7"/>
-      <c r="I131" s="84"/>
-      <c r="J131" s="84"/>
+      <c r="I131" s="24"/>
+      <c r="J131" s="24"/>
     </row>
     <row r="132" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="25" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="B132" s="78" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="C132" s="79"/>
       <c r="D132" s="22"/>
       <c r="E132" s="22"/>
       <c r="F132" s="80" t="s">
-        <v>800</v>
-      </c>
-      <c r="G132" s="73" t="s">
-        <v>261</v>
+        <v>749</v>
+      </c>
+      <c r="G132" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H132" s="7"/>
       <c r="I132" s="84"/>
@@ -6738,39 +6979,39 @@
     </row>
     <row r="133" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="25" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="B133" s="78" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="C133" s="79"/>
       <c r="D133" s="22"/>
       <c r="E133" s="22"/>
-      <c r="F133" s="80" t="s">
-        <v>357</v>
-      </c>
-      <c r="G133" s="73" t="s">
-        <v>261</v>
+      <c r="F133" s="73" t="s">
+        <v>750</v>
+      </c>
+      <c r="G133" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H133" s="7"/>
-      <c r="I133" s="84"/>
-      <c r="J133" s="84"/>
+      <c r="I133" s="24"/>
+      <c r="J133" s="24"/>
     </row>
     <row r="134" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="25" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="B134" s="78" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="C134" s="79"/>
       <c r="D134" s="22"/>
       <c r="E134" s="22"/>
       <c r="F134" s="80" t="s">
-        <v>756</v>
-      </c>
-      <c r="G134" s="80" t="s">
-        <v>129</v>
+        <v>342</v>
+      </c>
+      <c r="G134" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H134" s="7"/>
       <c r="I134" s="84"/>
@@ -6778,99 +7019,99 @@
     </row>
     <row r="135" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="25" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="B135" s="78" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="C135" s="79"/>
       <c r="D135" s="22"/>
       <c r="E135" s="22"/>
-      <c r="F135" s="73" t="s">
-        <v>757</v>
+      <c r="F135" s="80" t="s">
+        <v>345</v>
       </c>
       <c r="G135" s="80" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="H135" s="7"/>
-      <c r="I135" s="24"/>
-      <c r="J135" s="24"/>
+      <c r="I135" s="84"/>
+      <c r="J135" s="84"/>
     </row>
     <row r="136" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="25" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="B136" s="78" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="C136" s="79"/>
       <c r="D136" s="22"/>
       <c r="E136" s="22"/>
-      <c r="F136" s="73" t="s">
-        <v>758</v>
-      </c>
-      <c r="G136" s="23" t="s">
+      <c r="F136" s="80" t="s">
+        <v>751</v>
+      </c>
+      <c r="G136" s="80" t="s">
         <v>129</v>
       </c>
       <c r="H136" s="7"/>
-      <c r="I136" s="24"/>
-      <c r="J136" s="24"/>
+      <c r="I136" s="84"/>
+      <c r="J136" s="84"/>
     </row>
     <row r="137" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="25" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="B137" s="78" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C137" s="79"/>
       <c r="D137" s="22"/>
       <c r="E137" s="22"/>
-      <c r="F137" s="73" t="s">
-        <v>758</v>
-      </c>
-      <c r="G137" s="23" t="s">
-        <v>261</v>
+      <c r="F137" s="80" t="s">
+        <v>752</v>
+      </c>
+      <c r="G137" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H137" s="7"/>
-      <c r="I137" s="24"/>
-      <c r="J137" s="24"/>
+      <c r="I137" s="84"/>
+      <c r="J137" s="84"/>
     </row>
     <row r="138" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="25" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="B138" s="78" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="C138" s="79"/>
       <c r="D138" s="22"/>
       <c r="E138" s="22"/>
-      <c r="F138" s="73" t="s">
-        <v>759</v>
-      </c>
-      <c r="G138" s="23" t="s">
-        <v>261</v>
+      <c r="F138" s="80" t="s">
+        <v>797</v>
+      </c>
+      <c r="G138" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H138" s="7"/>
-      <c r="I138" s="24"/>
-      <c r="J138" s="24"/>
+      <c r="I138" s="84"/>
+      <c r="J138" s="84"/>
     </row>
     <row r="139" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="25" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="B139" s="78" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="C139" s="79"/>
       <c r="D139" s="22"/>
       <c r="E139" s="22"/>
       <c r="F139" s="80" t="s">
-        <v>760</v>
-      </c>
-      <c r="G139" s="80" t="s">
-        <v>129</v>
+        <v>356</v>
+      </c>
+      <c r="G139" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H139" s="7"/>
       <c r="I139" s="84"/>
@@ -6878,16 +7119,16 @@
     </row>
     <row r="140" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="25" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="B140" s="78" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="C140" s="79"/>
       <c r="D140" s="22"/>
       <c r="E140" s="22"/>
       <c r="F140" s="80" t="s">
-        <v>374</v>
+        <v>753</v>
       </c>
       <c r="G140" s="80" t="s">
         <v>129</v>
@@ -6898,134 +7139,136 @@
     </row>
     <row r="141" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="25" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="B141" s="78" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C141" s="79"/>
       <c r="D141" s="22"/>
       <c r="E141" s="22"/>
-      <c r="F141" s="80" t="s">
-        <v>377</v>
+      <c r="F141" s="73" t="s">
+        <v>754</v>
       </c>
       <c r="G141" s="80" t="s">
         <v>129</v>
       </c>
       <c r="H141" s="7"/>
-      <c r="I141" s="84"/>
-      <c r="J141" s="84"/>
+      <c r="I141" s="24"/>
+      <c r="J141" s="24"/>
     </row>
     <row r="142" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="25" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B142" s="78" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="C142" s="79"/>
       <c r="D142" s="22"/>
       <c r="E142" s="22"/>
-      <c r="F142" s="80" t="s">
-        <v>380</v>
-      </c>
-      <c r="G142" s="80" t="s">
+      <c r="F142" s="73" t="s">
+        <v>755</v>
+      </c>
+      <c r="G142" s="23" t="s">
         <v>129</v>
       </c>
       <c r="H142" s="7"/>
-      <c r="I142" s="84"/>
-      <c r="J142" s="84"/>
+      <c r="I142" s="24"/>
+      <c r="J142" s="24"/>
     </row>
     <row r="143" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="25" t="s">
-        <v>793</v>
+        <v>364</v>
       </c>
       <c r="B143" s="78" t="s">
-        <v>794</v>
+        <v>365</v>
       </c>
       <c r="C143" s="79"/>
       <c r="D143" s="22"/>
       <c r="E143" s="22"/>
-      <c r="F143" s="80"/>
-      <c r="G143" s="73" t="s">
-        <v>261</v>
+      <c r="F143" s="73" t="s">
+        <v>755</v>
+      </c>
+      <c r="G143" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H143" s="7"/>
-      <c r="I143" s="84"/>
-      <c r="J143" s="84"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="24"/>
     </row>
     <row r="144" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="25" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="B144" s="78" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C144" s="79"/>
       <c r="D144" s="22"/>
       <c r="E144" s="22"/>
-      <c r="F144" s="80" t="s">
-        <v>383</v>
-      </c>
-      <c r="G144" s="80" t="s">
-        <v>129</v>
+      <c r="F144" s="73" t="s">
+        <v>756</v>
+      </c>
+      <c r="G144" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H144" s="7"/>
-      <c r="I144" s="84"/>
-      <c r="J144" s="84"/>
+      <c r="I144" s="24"/>
+      <c r="J144" s="24"/>
     </row>
     <row r="145" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="25" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="B145" s="78" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="C145" s="79"/>
       <c r="D145" s="22"/>
       <c r="E145" s="22"/>
-      <c r="F145" s="29" t="s">
-        <v>386</v>
+      <c r="F145" s="80" t="s">
+        <v>757</v>
       </c>
       <c r="G145" s="80" t="s">
         <v>129</v>
       </c>
       <c r="H145" s="7"/>
-      <c r="I145" s="24"/>
-      <c r="J145" s="24"/>
+      <c r="I145" s="84"/>
+      <c r="J145" s="84"/>
     </row>
     <row r="146" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="25" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="B146" s="78" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C146" s="79"/>
       <c r="D146" s="22"/>
       <c r="E146" s="22"/>
-      <c r="F146" s="73" t="s">
-        <v>386</v>
-      </c>
-      <c r="G146" s="23" t="s">
-        <v>261</v>
+      <c r="F146" s="80" t="s">
+        <v>373</v>
+      </c>
+      <c r="G146" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H146" s="7"/>
-      <c r="I146" s="24"/>
-      <c r="J146" s="24"/>
+      <c r="I146" s="84"/>
+      <c r="J146" s="84"/>
     </row>
     <row r="147" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="25" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="B147" s="78" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="C147" s="79"/>
       <c r="D147" s="22"/>
       <c r="E147" s="22"/>
       <c r="F147" s="80" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="G147" s="80" t="s">
         <v>129</v>
@@ -7036,79 +7279,77 @@
     </row>
     <row r="148" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="25" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="B148" s="78" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="C148" s="79"/>
       <c r="D148" s="22"/>
       <c r="E148" s="22"/>
       <c r="F148" s="80" t="s">
-        <v>761</v>
+        <v>379</v>
       </c>
       <c r="G148" s="80" t="s">
         <v>129</v>
       </c>
       <c r="H148" s="7"/>
-      <c r="I148" s="24"/>
-      <c r="J148" s="24"/>
+      <c r="I148" s="84"/>
+      <c r="J148" s="84"/>
     </row>
     <row r="149" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="25" t="s">
-        <v>395</v>
+        <v>790</v>
       </c>
       <c r="B149" s="78" t="s">
-        <v>396</v>
+        <v>791</v>
       </c>
       <c r="C149" s="79"/>
       <c r="D149" s="22"/>
       <c r="E149" s="22"/>
-      <c r="F149" s="80" t="s">
-        <v>397</v>
-      </c>
-      <c r="G149" s="80" t="s">
-        <v>129</v>
+      <c r="F149" s="80"/>
+      <c r="G149" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H149" s="7"/>
-      <c r="I149" s="24"/>
-      <c r="J149" s="24"/>
+      <c r="I149" s="84"/>
+      <c r="J149" s="84"/>
     </row>
     <row r="150" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="25" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="B150" s="78" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="C150" s="79"/>
       <c r="D150" s="22"/>
       <c r="E150" s="22"/>
       <c r="F150" s="80" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="G150" s="80" t="s">
         <v>129</v>
       </c>
       <c r="H150" s="7"/>
-      <c r="I150" s="24"/>
-      <c r="J150" s="24"/>
+      <c r="I150" s="84"/>
+      <c r="J150" s="84"/>
     </row>
     <row r="151" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="25" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="B151" s="78" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="C151" s="79"/>
       <c r="D151" s="22"/>
       <c r="E151" s="22"/>
-      <c r="F151" s="80" t="s">
-        <v>762</v>
-      </c>
-      <c r="G151" s="73" t="s">
-        <v>15</v>
+      <c r="F151" s="29" t="s">
+        <v>385</v>
+      </c>
+      <c r="G151" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H151" s="7"/>
       <c r="I151" s="24"/>
@@ -7116,19 +7357,19 @@
     </row>
     <row r="152" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="25" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="B152" s="78" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="C152" s="79"/>
       <c r="D152" s="22"/>
       <c r="E152" s="22"/>
-      <c r="F152" s="80" t="s">
-        <v>405</v>
-      </c>
-      <c r="G152" s="80" t="s">
-        <v>129</v>
+      <c r="F152" s="73" t="s">
+        <v>385</v>
+      </c>
+      <c r="G152" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H152" s="7"/>
       <c r="I152" s="24"/>
@@ -7136,36 +7377,36 @@
     </row>
     <row r="153" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="25" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="B153" s="78" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="C153" s="79"/>
       <c r="D153" s="22"/>
       <c r="E153" s="22"/>
       <c r="F153" s="80" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="G153" s="80" t="s">
         <v>129</v>
       </c>
       <c r="H153" s="7"/>
-      <c r="I153" s="24"/>
-      <c r="J153" s="24"/>
+      <c r="I153" s="84"/>
+      <c r="J153" s="84"/>
     </row>
     <row r="154" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="25" t="s">
-        <v>820</v>
+        <v>391</v>
       </c>
       <c r="B154" s="78" t="s">
-        <v>821</v>
+        <v>392</v>
       </c>
       <c r="C154" s="79"/>
       <c r="D154" s="22"/>
       <c r="E154" s="22"/>
       <c r="F154" s="80" t="s">
-        <v>822</v>
+        <v>758</v>
       </c>
       <c r="G154" s="80" t="s">
         <v>129</v>
@@ -7176,18 +7417,18 @@
     </row>
     <row r="155" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="25" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B155" s="78" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="C155" s="79"/>
       <c r="D155" s="22"/>
       <c r="E155" s="22"/>
-      <c r="F155" s="73" t="s">
-        <v>720</v>
-      </c>
-      <c r="G155" s="23" t="s">
+      <c r="F155" s="80" t="s">
+        <v>396</v>
+      </c>
+      <c r="G155" s="80" t="s">
         <v>129</v>
       </c>
       <c r="H155" s="7"/>
@@ -7196,59 +7437,59 @@
     </row>
     <row r="156" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="25" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="B156" s="78" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="C156" s="79"/>
       <c r="D156" s="22"/>
       <c r="E156" s="22"/>
-      <c r="F156" s="29" t="s">
-        <v>763</v>
+      <c r="F156" s="80" t="s">
+        <v>399</v>
       </c>
       <c r="G156" s="80" t="s">
         <v>129</v>
       </c>
-      <c r="H156" s="85"/>
+      <c r="H156" s="7"/>
       <c r="I156" s="24"/>
       <c r="J156" s="24"/>
     </row>
     <row r="157" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="25" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B157" s="78" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C157" s="79"/>
       <c r="D157" s="22"/>
       <c r="E157" s="22"/>
-      <c r="F157" s="73" t="s">
-        <v>740</v>
-      </c>
-      <c r="G157" s="80" t="s">
-        <v>129</v>
-      </c>
-      <c r="H157" s="85"/>
+      <c r="F157" s="80" t="s">
+        <v>759</v>
+      </c>
+      <c r="G157" s="192" t="s">
+        <v>15</v>
+      </c>
+      <c r="H157" s="7"/>
       <c r="I157" s="24"/>
       <c r="J157" s="24"/>
     </row>
     <row r="158" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="25" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="B158" s="78" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="C158" s="79"/>
       <c r="D158" s="22"/>
       <c r="E158" s="22"/>
-      <c r="F158" s="73" t="s">
-        <v>740</v>
-      </c>
-      <c r="G158" s="23" t="s">
-        <v>261</v>
+      <c r="F158" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="G158" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H158" s="7"/>
       <c r="I158" s="24"/>
@@ -7256,19 +7497,19 @@
     </row>
     <row r="159" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="25" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B159" s="78" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="C159" s="79"/>
       <c r="D159" s="22"/>
       <c r="E159" s="22"/>
-      <c r="F159" s="73" t="s">
-        <v>721</v>
-      </c>
-      <c r="G159" s="23" t="s">
-        <v>261</v>
+      <c r="F159" s="80" t="s">
+        <v>407</v>
+      </c>
+      <c r="G159" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H159" s="7"/>
       <c r="I159" s="24"/>
@@ -7276,19 +7517,19 @@
     </row>
     <row r="160" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="25" t="s">
-        <v>419</v>
+        <v>817</v>
       </c>
       <c r="B160" s="78" t="s">
-        <v>420</v>
+        <v>818</v>
       </c>
       <c r="C160" s="79"/>
       <c r="D160" s="22"/>
       <c r="E160" s="22"/>
-      <c r="F160" s="73" t="s">
-        <v>722</v>
-      </c>
-      <c r="G160" s="23" t="s">
-        <v>261</v>
+      <c r="F160" s="80" t="s">
+        <v>819</v>
+      </c>
+      <c r="G160" s="80" t="s">
+        <v>260</v>
       </c>
       <c r="H160" s="7"/>
       <c r="I160" s="24"/>
@@ -7296,19 +7537,19 @@
     </row>
     <row r="161" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="25" t="s">
-        <v>823</v>
+        <v>408</v>
       </c>
       <c r="B161" s="78" t="s">
-        <v>824</v>
+        <v>409</v>
       </c>
       <c r="C161" s="79"/>
       <c r="D161" s="22"/>
       <c r="E161" s="22"/>
       <c r="F161" s="73" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="G161" s="23" t="s">
-        <v>261</v>
+        <v>129</v>
       </c>
       <c r="H161" s="7"/>
       <c r="I161" s="24"/>
@@ -7316,59 +7557,59 @@
     </row>
     <row r="162" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="25" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="B162" s="78" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="C162" s="79"/>
       <c r="D162" s="22"/>
       <c r="E162" s="22"/>
       <c r="F162" s="29" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="G162" s="80" t="s">
         <v>129</v>
       </c>
-      <c r="H162" s="7"/>
+      <c r="H162" s="85"/>
       <c r="I162" s="24"/>
       <c r="J162" s="24"/>
     </row>
     <row r="163" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="25" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B163" s="78" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C163" s="79"/>
       <c r="D163" s="22"/>
       <c r="E163" s="22"/>
-      <c r="F163" s="80" t="s">
-        <v>765</v>
+      <c r="F163" s="73" t="s">
+        <v>737</v>
       </c>
       <c r="G163" s="80" t="s">
         <v>129</v>
       </c>
-      <c r="H163" s="7"/>
+      <c r="H163" s="85"/>
       <c r="I163" s="24"/>
       <c r="J163" s="24"/>
     </row>
     <row r="164" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="25" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="B164" s="78" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="C164" s="79"/>
       <c r="D164" s="22"/>
       <c r="E164" s="22"/>
       <c r="F164" s="73" t="s">
-        <v>766</v>
+        <v>737</v>
       </c>
       <c r="G164" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H164" s="7"/>
       <c r="I164" s="24"/>
@@ -7376,19 +7617,19 @@
     </row>
     <row r="165" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="25" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="B165" s="78" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C165" s="79"/>
       <c r="D165" s="22"/>
       <c r="E165" s="22"/>
       <c r="F165" s="73" t="s">
-        <v>766</v>
+        <v>719</v>
       </c>
       <c r="G165" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H165" s="7"/>
       <c r="I165" s="24"/>
@@ -7396,19 +7637,19 @@
     </row>
     <row r="166" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="25" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B166" s="78" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="C166" s="79"/>
       <c r="D166" s="22"/>
       <c r="E166" s="22"/>
-      <c r="F166" s="80" t="s">
-        <v>432</v>
-      </c>
-      <c r="G166" s="73" t="s">
-        <v>261</v>
+      <c r="F166" s="73" t="s">
+        <v>720</v>
+      </c>
+      <c r="G166" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H166" s="7"/>
       <c r="I166" s="24"/>
@@ -7416,19 +7657,19 @@
     </row>
     <row r="167" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="25" t="s">
-        <v>433</v>
+        <v>820</v>
       </c>
       <c r="B167" s="78" t="s">
-        <v>434</v>
+        <v>821</v>
       </c>
       <c r="C167" s="79"/>
       <c r="D167" s="22"/>
       <c r="E167" s="22"/>
-      <c r="F167" s="80" t="s">
-        <v>435</v>
-      </c>
-      <c r="G167" s="73" t="s">
-        <v>261</v>
+      <c r="F167" s="73" t="s">
+        <v>720</v>
+      </c>
+      <c r="G167" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H167" s="7"/>
       <c r="I167" s="24"/>
@@ -7436,19 +7677,19 @@
     </row>
     <row r="168" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="25" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="B168" s="78" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="C168" s="79"/>
       <c r="D168" s="22"/>
       <c r="E168" s="22"/>
-      <c r="F168" s="73" t="s">
-        <v>723</v>
-      </c>
-      <c r="G168" s="23" t="s">
-        <v>261</v>
+      <c r="F168" s="29" t="s">
+        <v>761</v>
+      </c>
+      <c r="G168" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H168" s="7"/>
       <c r="I168" s="24"/>
@@ -7456,19 +7697,19 @@
     </row>
     <row r="169" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="25" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="B169" s="78" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="C169" s="79"/>
       <c r="D169" s="22"/>
       <c r="E169" s="22"/>
-      <c r="F169" s="73" t="s">
-        <v>724</v>
-      </c>
-      <c r="G169" s="23" t="s">
-        <v>261</v>
+      <c r="F169" s="80" t="s">
+        <v>762</v>
+      </c>
+      <c r="G169" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H169" s="7"/>
       <c r="I169" s="24"/>
@@ -7476,19 +7717,19 @@
     </row>
     <row r="170" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="25" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="B170" s="78" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="C170" s="79"/>
       <c r="D170" s="22"/>
       <c r="E170" s="22"/>
       <c r="F170" s="73" t="s">
-        <v>724</v>
+        <v>763</v>
       </c>
       <c r="G170" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H170" s="7"/>
       <c r="I170" s="24"/>
@@ -7496,19 +7737,19 @@
     </row>
     <row r="171" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="25" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="B171" s="78" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="C171" s="79"/>
       <c r="D171" s="22"/>
       <c r="E171" s="22"/>
-      <c r="F171" s="86" t="s">
-        <v>444</v>
-      </c>
-      <c r="G171" s="73" t="s">
-        <v>261</v>
+      <c r="F171" s="73" t="s">
+        <v>763</v>
+      </c>
+      <c r="G171" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H171" s="7"/>
       <c r="I171" s="24"/>
@@ -7516,19 +7757,19 @@
     </row>
     <row r="172" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="25" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="B172" s="78" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="C172" s="79"/>
       <c r="D172" s="22"/>
       <c r="E172" s="22"/>
       <c r="F172" s="80" t="s">
-        <v>725</v>
+        <v>431</v>
       </c>
       <c r="G172" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H172" s="7"/>
       <c r="I172" s="24"/>
@@ -7536,19 +7777,19 @@
     </row>
     <row r="173" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="25" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="B173" s="78" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="C173" s="79"/>
       <c r="D173" s="22"/>
       <c r="E173" s="22"/>
-      <c r="F173" s="73" t="s">
-        <v>713</v>
-      </c>
-      <c r="G173" s="23" t="s">
-        <v>261</v>
+      <c r="F173" s="80" t="s">
+        <v>434</v>
+      </c>
+      <c r="G173" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H173" s="7"/>
       <c r="I173" s="24"/>
@@ -7556,19 +7797,19 @@
     </row>
     <row r="174" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="25" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="B174" s="78" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="C174" s="79"/>
       <c r="D174" s="22"/>
       <c r="E174" s="22"/>
-      <c r="F174" s="80" t="s">
-        <v>451</v>
-      </c>
-      <c r="G174" s="73" t="s">
-        <v>261</v>
+      <c r="F174" s="73" t="s">
+        <v>721</v>
+      </c>
+      <c r="G174" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H174" s="7"/>
       <c r="I174" s="24"/>
@@ -7576,19 +7817,19 @@
     </row>
     <row r="175" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="25" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="B175" s="78" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="C175" s="79"/>
       <c r="D175" s="22"/>
       <c r="E175" s="22"/>
       <c r="F175" s="73" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="G175" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H175" s="7"/>
       <c r="I175" s="24"/>
@@ -7596,19 +7837,19 @@
     </row>
     <row r="176" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="25" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="B176" s="78" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="C176" s="79"/>
       <c r="D176" s="22"/>
       <c r="E176" s="22"/>
       <c r="F176" s="73" t="s">
-        <v>767</v>
+        <v>722</v>
       </c>
       <c r="G176" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H176" s="7"/>
       <c r="I176" s="24"/>
@@ -7616,19 +7857,19 @@
     </row>
     <row r="177" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="25" t="s">
-        <v>813</v>
+        <v>441</v>
       </c>
       <c r="B177" s="78" t="s">
-        <v>814</v>
+        <v>442</v>
       </c>
       <c r="C177" s="79"/>
       <c r="D177" s="22"/>
       <c r="E177" s="22"/>
-      <c r="F177" s="73" t="s">
-        <v>767</v>
-      </c>
-      <c r="G177" s="23" t="s">
-        <v>261</v>
+      <c r="F177" s="86" t="s">
+        <v>443</v>
+      </c>
+      <c r="G177" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H177" s="7"/>
       <c r="I177" s="24"/>
@@ -7636,19 +7877,19 @@
     </row>
     <row r="178" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="25" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="B178" s="78" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="C178" s="79"/>
       <c r="D178" s="22"/>
       <c r="E178" s="22"/>
-      <c r="F178" s="73" t="s">
-        <v>741</v>
-      </c>
-      <c r="G178" s="23" t="s">
-        <v>261</v>
+      <c r="F178" s="80" t="s">
+        <v>723</v>
+      </c>
+      <c r="G178" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H178" s="7"/>
       <c r="I178" s="24"/>
@@ -7656,19 +7897,19 @@
     </row>
     <row r="179" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="25" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B179" s="78" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="C179" s="79"/>
       <c r="D179" s="22"/>
       <c r="E179" s="22"/>
       <c r="F179" s="73" t="s">
-        <v>741</v>
+        <v>712</v>
       </c>
       <c r="G179" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H179" s="7"/>
       <c r="I179" s="24"/>
@@ -7676,19 +7917,19 @@
     </row>
     <row r="180" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="25" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B180" s="78" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C180" s="79"/>
       <c r="D180" s="22"/>
       <c r="E180" s="22"/>
       <c r="F180" s="80" t="s">
-        <v>777</v>
+        <v>450</v>
       </c>
       <c r="G180" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H180" s="7"/>
       <c r="I180" s="24"/>
@@ -7696,19 +7937,19 @@
     </row>
     <row r="181" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="25" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="B181" s="78" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="C181" s="79"/>
       <c r="D181" s="22"/>
       <c r="E181" s="22"/>
-      <c r="F181" s="80" t="s">
-        <v>778</v>
-      </c>
-      <c r="G181" s="73" t="s">
-        <v>261</v>
+      <c r="F181" s="73" t="s">
+        <v>724</v>
+      </c>
+      <c r="G181" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H181" s="7"/>
       <c r="I181" s="24"/>
@@ -7716,19 +7957,19 @@
     </row>
     <row r="182" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="25" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="B182" s="78" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="C182" s="79"/>
       <c r="D182" s="22"/>
       <c r="E182" s="22"/>
-      <c r="F182" s="80" t="s">
-        <v>779</v>
-      </c>
-      <c r="G182" s="80" t="s">
-        <v>129</v>
+      <c r="F182" s="73" t="s">
+        <v>764</v>
+      </c>
+      <c r="G182" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H182" s="7"/>
       <c r="I182" s="24"/>
@@ -7736,19 +7977,19 @@
     </row>
     <row r="183" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="25" t="s">
-        <v>469</v>
+        <v>810</v>
       </c>
       <c r="B183" s="78" t="s">
-        <v>470</v>
+        <v>811</v>
       </c>
       <c r="C183" s="79"/>
       <c r="D183" s="22"/>
       <c r="E183" s="22"/>
       <c r="F183" s="73" t="s">
-        <v>742</v>
+        <v>764</v>
       </c>
       <c r="G183" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H183" s="7"/>
       <c r="I183" s="24"/>
@@ -7756,59 +7997,59 @@
     </row>
     <row r="184" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="25" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="B184" s="78" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="C184" s="79"/>
       <c r="D184" s="22"/>
       <c r="E184" s="22"/>
-      <c r="F184" s="80" t="s">
-        <v>473</v>
-      </c>
-      <c r="G184" s="80" t="s">
-        <v>129</v>
+      <c r="F184" s="73" t="s">
+        <v>738</v>
+      </c>
+      <c r="G184" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H184" s="7"/>
       <c r="I184" s="24"/>
       <c r="J184" s="24"/>
     </row>
-    <row r="185" spans="1:10" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="25" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="B185" s="78" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="C185" s="79"/>
       <c r="D185" s="22"/>
       <c r="E185" s="22"/>
       <c r="F185" s="73" t="s">
-        <v>727</v>
+        <v>738</v>
       </c>
       <c r="G185" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="H185" s="87"/>
+        <v>260</v>
+      </c>
+      <c r="H185" s="7"/>
       <c r="I185" s="24"/>
       <c r="J185" s="24"/>
     </row>
     <row r="186" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="25" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="B186" s="78" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="C186" s="79"/>
       <c r="D186" s="22"/>
       <c r="E186" s="22"/>
-      <c r="F186" s="73" t="s">
-        <v>727</v>
-      </c>
-      <c r="G186" s="23" t="s">
-        <v>261</v>
+      <c r="F186" s="80" t="s">
+        <v>774</v>
+      </c>
+      <c r="G186" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H186" s="7"/>
       <c r="I186" s="24"/>
@@ -7816,19 +8057,19 @@
     </row>
     <row r="187" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="25" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="B187" s="78" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="C187" s="79"/>
       <c r="D187" s="22"/>
       <c r="E187" s="22"/>
-      <c r="F187" s="73" t="s">
-        <v>728</v>
-      </c>
-      <c r="G187" s="23" t="s">
-        <v>261</v>
+      <c r="F187" s="80" t="s">
+        <v>775</v>
+      </c>
+      <c r="G187" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H187" s="7"/>
       <c r="I187" s="24"/>
@@ -7836,10 +8077,10 @@
     </row>
     <row r="188" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="25" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="B188" s="78" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="C188" s="79"/>
       <c r="D188" s="22"/>
@@ -7856,19 +8097,19 @@
     </row>
     <row r="189" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="25" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="B189" s="78" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="C189" s="79"/>
       <c r="D189" s="22"/>
       <c r="E189" s="22"/>
       <c r="F189" s="73" t="s">
-        <v>712</v>
+        <v>739</v>
       </c>
       <c r="G189" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H189" s="7"/>
       <c r="I189" s="24"/>
@@ -7876,59 +8117,59 @@
     </row>
     <row r="190" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="25" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="B190" s="78" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="C190" s="79"/>
       <c r="D190" s="22"/>
       <c r="E190" s="22"/>
       <c r="F190" s="80" t="s">
-        <v>487</v>
-      </c>
-      <c r="G190" s="73" t="s">
-        <v>261</v>
+        <v>472</v>
+      </c>
+      <c r="G190" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H190" s="7"/>
       <c r="I190" s="24"/>
       <c r="J190" s="24"/>
     </row>
-    <row r="191" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A191" s="25" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="B191" s="78" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="C191" s="79"/>
       <c r="D191" s="22"/>
       <c r="E191" s="22"/>
-      <c r="F191" s="80" t="s">
-        <v>490</v>
-      </c>
-      <c r="G191" s="73" t="s">
-        <v>261</v>
-      </c>
-      <c r="H191" s="7"/>
+      <c r="F191" s="73" t="s">
+        <v>855</v>
+      </c>
+      <c r="G191" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="H191" s="87"/>
       <c r="I191" s="24"/>
       <c r="J191" s="24"/>
     </row>
     <row r="192" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="25" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="B192" s="78" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="C192" s="79"/>
       <c r="D192" s="22"/>
       <c r="E192" s="22"/>
-      <c r="F192" s="80" t="s">
-        <v>493</v>
-      </c>
-      <c r="G192" s="73" t="s">
-        <v>261</v>
+      <c r="F192" s="73" t="s">
+        <v>856</v>
+      </c>
+      <c r="G192" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H192" s="7"/>
       <c r="I192" s="24"/>
@@ -7936,19 +8177,19 @@
     </row>
     <row r="193" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="25" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="B193" s="78" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="C193" s="79"/>
       <c r="D193" s="22"/>
       <c r="E193" s="22"/>
       <c r="F193" s="73" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="G193" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H193" s="7"/>
       <c r="I193" s="24"/>
@@ -7956,19 +8197,19 @@
     </row>
     <row r="194" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="25" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="B194" s="78" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="C194" s="79"/>
       <c r="D194" s="22"/>
       <c r="E194" s="22"/>
-      <c r="F194" s="73" t="s">
-        <v>730</v>
-      </c>
-      <c r="G194" s="23" t="s">
-        <v>261</v>
+      <c r="F194" s="80" t="s">
+        <v>773</v>
+      </c>
+      <c r="G194" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H194" s="7"/>
       <c r="I194" s="24"/>
@@ -7976,19 +8217,19 @@
     </row>
     <row r="195" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="25" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="B195" s="78" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="C195" s="79"/>
       <c r="D195" s="22"/>
       <c r="E195" s="22"/>
       <c r="F195" s="73" t="s">
-        <v>731</v>
+        <v>711</v>
       </c>
       <c r="G195" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H195" s="7"/>
       <c r="I195" s="24"/>
@@ -7996,19 +8237,19 @@
     </row>
     <row r="196" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="25" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="B196" s="78" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="C196" s="79"/>
       <c r="D196" s="22"/>
       <c r="E196" s="22"/>
-      <c r="F196" s="73" t="s">
-        <v>732</v>
-      </c>
-      <c r="G196" s="23" t="s">
-        <v>261</v>
+      <c r="F196" s="80" t="s">
+        <v>486</v>
+      </c>
+      <c r="G196" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H196" s="7"/>
       <c r="I196" s="24"/>
@@ -8016,19 +8257,19 @@
     </row>
     <row r="197" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="25" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="B197" s="78" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="C197" s="79"/>
       <c r="D197" s="22"/>
       <c r="E197" s="22"/>
-      <c r="F197" s="73" t="s">
-        <v>733</v>
-      </c>
-      <c r="G197" s="23" t="s">
-        <v>261</v>
+      <c r="F197" s="80" t="s">
+        <v>489</v>
+      </c>
+      <c r="G197" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H197" s="7"/>
       <c r="I197" s="24"/>
@@ -8036,59 +8277,59 @@
     </row>
     <row r="198" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="25" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="B198" s="78" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="C198" s="79"/>
       <c r="D198" s="22"/>
       <c r="E198" s="22"/>
-      <c r="F198" s="29" t="s">
-        <v>506</v>
-      </c>
-      <c r="G198" s="23" t="s">
-        <v>261</v>
+      <c r="F198" s="80" t="s">
+        <v>492</v>
+      </c>
+      <c r="G198" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H198" s="7"/>
       <c r="I198" s="24"/>
       <c r="J198" s="24"/>
     </row>
-    <row r="199" spans="1:10" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="25" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="B199" s="78" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C199" s="79"/>
       <c r="D199" s="22"/>
       <c r="E199" s="22"/>
       <c r="F199" s="73" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="G199" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="H199" s="88"/>
+        <v>260</v>
+      </c>
+      <c r="H199" s="7"/>
       <c r="I199" s="24"/>
       <c r="J199" s="24"/>
     </row>
     <row r="200" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="25" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="B200" s="78" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="C200" s="79"/>
       <c r="D200" s="22"/>
       <c r="E200" s="22"/>
-      <c r="F200" s="80" t="s">
-        <v>511</v>
-      </c>
-      <c r="G200" s="73" t="s">
-        <v>261</v>
+      <c r="F200" s="73" t="s">
+        <v>727</v>
+      </c>
+      <c r="G200" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H200" s="7"/>
       <c r="I200" s="24"/>
@@ -8096,19 +8337,19 @@
     </row>
     <row r="201" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="25" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="B201" s="78" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="C201" s="79"/>
       <c r="D201" s="22"/>
       <c r="E201" s="22"/>
       <c r="F201" s="73" t="s">
-        <v>743</v>
+        <v>728</v>
       </c>
       <c r="G201" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H201" s="7"/>
       <c r="I201" s="24"/>
@@ -8116,19 +8357,19 @@
     </row>
     <row r="202" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="25" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="B202" s="78" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="C202" s="79"/>
       <c r="D202" s="22"/>
       <c r="E202" s="22"/>
-      <c r="F202" s="80" t="s">
-        <v>516</v>
-      </c>
-      <c r="G202" s="73" t="s">
-        <v>261</v>
+      <c r="F202" s="73" t="s">
+        <v>729</v>
+      </c>
+      <c r="G202" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H202" s="7"/>
       <c r="I202" s="24"/>
@@ -8136,19 +8377,19 @@
     </row>
     <row r="203" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="25" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="B203" s="78" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="C203" s="79"/>
       <c r="D203" s="22"/>
       <c r="E203" s="22"/>
       <c r="F203" s="73" t="s">
-        <v>768</v>
+        <v>730</v>
       </c>
       <c r="G203" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H203" s="7"/>
       <c r="I203" s="24"/>
@@ -8156,59 +8397,59 @@
     </row>
     <row r="204" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="25" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="B204" s="78" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="C204" s="79"/>
       <c r="D204" s="22"/>
       <c r="E204" s="22"/>
-      <c r="F204" s="73" t="s">
-        <v>523</v>
+      <c r="F204" s="29" t="s">
+        <v>505</v>
       </c>
       <c r="G204" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H204" s="7"/>
       <c r="I204" s="24"/>
       <c r="J204" s="24"/>
     </row>
-    <row r="205" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A205" s="25" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="B205" s="78" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="C205" s="79"/>
       <c r="D205" s="22"/>
       <c r="E205" s="22"/>
-      <c r="F205" s="80" t="s">
-        <v>523</v>
-      </c>
-      <c r="G205" s="80" t="s">
-        <v>129</v>
-      </c>
-      <c r="H205" s="7"/>
+      <c r="F205" s="73" t="s">
+        <v>731</v>
+      </c>
+      <c r="G205" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="H205" s="88"/>
       <c r="I205" s="24"/>
       <c r="J205" s="24"/>
     </row>
     <row r="206" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="25" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="B206" s="78" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="C206" s="79"/>
       <c r="D206" s="22"/>
       <c r="E206" s="22"/>
-      <c r="F206" s="73" t="s">
-        <v>769</v>
-      </c>
-      <c r="G206" s="23" t="s">
-        <v>261</v>
+      <c r="F206" s="80" t="s">
+        <v>510</v>
+      </c>
+      <c r="G206" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H206" s="7"/>
       <c r="I206" s="24"/>
@@ -8216,19 +8457,19 @@
     </row>
     <row r="207" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="25" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="B207" s="78" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="C207" s="79"/>
       <c r="D207" s="22"/>
       <c r="E207" s="22"/>
       <c r="F207" s="73" t="s">
-        <v>769</v>
-      </c>
-      <c r="G207" s="80" t="s">
-        <v>261</v>
+        <v>740</v>
+      </c>
+      <c r="G207" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H207" s="7"/>
       <c r="I207" s="24"/>
@@ -8236,19 +8477,19 @@
     </row>
     <row r="208" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="25" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="B208" s="78" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="C208" s="79"/>
       <c r="D208" s="22"/>
       <c r="E208" s="22"/>
       <c r="F208" s="80" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="G208" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H208" s="7"/>
       <c r="I208" s="24"/>
@@ -8256,19 +8497,19 @@
     </row>
     <row r="209" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="25" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="B209" s="78" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="C209" s="79"/>
       <c r="D209" s="22"/>
       <c r="E209" s="22"/>
-      <c r="F209" s="80" t="s">
-        <v>533</v>
-      </c>
-      <c r="G209" s="73" t="s">
-        <v>261</v>
+      <c r="F209" s="73" t="s">
+        <v>765</v>
+      </c>
+      <c r="G209" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H209" s="7"/>
       <c r="I209" s="24"/>
@@ -8276,19 +8517,19 @@
     </row>
     <row r="210" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="25" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="B210" s="78" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="C210" s="79"/>
       <c r="D210" s="22"/>
       <c r="E210" s="22"/>
-      <c r="F210" s="80" t="s">
-        <v>536</v>
-      </c>
-      <c r="G210" s="80" t="s">
-        <v>129</v>
+      <c r="F210" s="73" t="s">
+        <v>522</v>
+      </c>
+      <c r="G210" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H210" s="7"/>
       <c r="I210" s="24"/>
@@ -8296,19 +8537,19 @@
     </row>
     <row r="211" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="25" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="B211" s="78" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="C211" s="79"/>
       <c r="D211" s="22"/>
       <c r="E211" s="22"/>
       <c r="F211" s="80" t="s">
-        <v>539</v>
-      </c>
-      <c r="G211" s="73" t="s">
-        <v>261</v>
+        <v>522</v>
+      </c>
+      <c r="G211" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H211" s="7"/>
       <c r="I211" s="24"/>
@@ -8316,19 +8557,19 @@
     </row>
     <row r="212" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="25" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="B212" s="78" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="C212" s="79"/>
       <c r="D212" s="22"/>
       <c r="E212" s="22"/>
-      <c r="F212" s="29" t="s">
-        <v>770</v>
+      <c r="F212" s="73" t="s">
+        <v>766</v>
       </c>
       <c r="G212" s="23" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="H212" s="7"/>
       <c r="I212" s="24"/>
@@ -8336,19 +8577,19 @@
     </row>
     <row r="213" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="25" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="B213" s="78" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="C213" s="79"/>
       <c r="D213" s="22"/>
       <c r="E213" s="22"/>
       <c r="F213" s="73" t="s">
-        <v>715</v>
-      </c>
-      <c r="G213" s="23" t="s">
-        <v>261</v>
+        <v>766</v>
+      </c>
+      <c r="G213" s="80" t="s">
+        <v>260</v>
       </c>
       <c r="H213" s="7"/>
       <c r="I213" s="24"/>
@@ -8356,19 +8597,19 @@
     </row>
     <row r="214" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="25" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="B214" s="78" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="C214" s="79"/>
       <c r="D214" s="22"/>
       <c r="E214" s="22"/>
-      <c r="F214" s="73" t="s">
-        <v>715</v>
-      </c>
-      <c r="G214" s="23" t="s">
-        <v>261</v>
+      <c r="F214" s="80" t="s">
+        <v>529</v>
+      </c>
+      <c r="G214" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H214" s="7"/>
       <c r="I214" s="24"/>
@@ -8376,19 +8617,19 @@
     </row>
     <row r="215" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="25" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="B215" s="78" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="C215" s="79"/>
       <c r="D215" s="22"/>
       <c r="E215" s="22"/>
-      <c r="F215" s="73" t="s">
-        <v>744</v>
-      </c>
-      <c r="G215" s="23" t="s">
-        <v>261</v>
+      <c r="F215" s="80" t="s">
+        <v>532</v>
+      </c>
+      <c r="G215" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H215" s="7"/>
       <c r="I215" s="24"/>
@@ -8396,19 +8637,19 @@
     </row>
     <row r="216" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="25" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="B216" s="78" t="s">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="C216" s="79"/>
       <c r="D216" s="22"/>
       <c r="E216" s="22"/>
-      <c r="F216" s="73" t="s">
-        <v>745</v>
-      </c>
-      <c r="G216" s="23" t="s">
-        <v>261</v>
+      <c r="F216" s="80" t="s">
+        <v>535</v>
+      </c>
+      <c r="G216" s="80" t="s">
+        <v>129</v>
       </c>
       <c r="H216" s="7"/>
       <c r="I216" s="24"/>
@@ -8416,19 +8657,19 @@
     </row>
     <row r="217" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="25" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="B217" s="78" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="C217" s="79"/>
       <c r="D217" s="22"/>
       <c r="E217" s="22"/>
-      <c r="F217" s="73" t="s">
-        <v>746</v>
-      </c>
-      <c r="G217" s="23" t="s">
-        <v>261</v>
+      <c r="F217" s="80" t="s">
+        <v>538</v>
+      </c>
+      <c r="G217" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H217" s="7"/>
       <c r="I217" s="24"/>
@@ -8436,19 +8677,19 @@
     </row>
     <row r="218" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="25" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="B218" s="78" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="C218" s="79"/>
       <c r="D218" s="22"/>
       <c r="E218" s="22"/>
-      <c r="F218" s="73" t="s">
-        <v>745</v>
+      <c r="F218" s="29" t="s">
+        <v>767</v>
       </c>
       <c r="G218" s="23" t="s">
-        <v>261</v>
+        <v>129</v>
       </c>
       <c r="H218" s="7"/>
       <c r="I218" s="24"/>
@@ -8456,19 +8697,19 @@
     </row>
     <row r="219" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="25" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="B219" s="78" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="C219" s="79"/>
       <c r="D219" s="22"/>
       <c r="E219" s="22"/>
       <c r="F219" s="73" t="s">
-        <v>772</v>
+        <v>714</v>
       </c>
       <c r="G219" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H219" s="7"/>
       <c r="I219" s="24"/>
@@ -8476,19 +8717,19 @@
     </row>
     <row r="220" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="25" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="B220" s="78" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="C220" s="79"/>
       <c r="D220" s="22"/>
       <c r="E220" s="22"/>
       <c r="F220" s="73" t="s">
-        <v>771</v>
+        <v>714</v>
       </c>
       <c r="G220" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H220" s="7"/>
       <c r="I220" s="24"/>
@@ -8496,19 +8737,19 @@
     </row>
     <row r="221" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="25" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="B221" s="78" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="C221" s="79"/>
       <c r="D221" s="22"/>
       <c r="E221" s="22"/>
       <c r="F221" s="73" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="G221" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H221" s="7"/>
       <c r="I221" s="24"/>
@@ -8516,19 +8757,19 @@
     </row>
     <row r="222" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="25" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="B222" s="78" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="C222" s="79"/>
       <c r="D222" s="22"/>
       <c r="E222" s="22"/>
-      <c r="F222" s="80" t="s">
-        <v>562</v>
-      </c>
-      <c r="G222" s="73" t="s">
-        <v>261</v>
+      <c r="F222" s="73" t="s">
+        <v>742</v>
+      </c>
+      <c r="G222" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H222" s="7"/>
       <c r="I222" s="24"/>
@@ -8536,19 +8777,19 @@
     </row>
     <row r="223" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="25" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="B223" s="78" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="C223" s="79"/>
       <c r="D223" s="22"/>
       <c r="E223" s="22"/>
-      <c r="F223" s="89" t="s">
-        <v>565</v>
-      </c>
-      <c r="G223" s="73" t="s">
-        <v>261</v>
+      <c r="F223" s="73" t="s">
+        <v>743</v>
+      </c>
+      <c r="G223" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H223" s="7"/>
       <c r="I223" s="24"/>
@@ -8556,19 +8797,19 @@
     </row>
     <row r="224" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="25" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="B224" s="78" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="C224" s="79"/>
       <c r="D224" s="22"/>
       <c r="E224" s="22"/>
       <c r="F224" s="73" t="s">
-        <v>773</v>
+        <v>742</v>
       </c>
       <c r="G224" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H224" s="7"/>
       <c r="I224" s="24"/>
@@ -8576,19 +8817,19 @@
     </row>
     <row r="225" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="25" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="B225" s="78" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="C225" s="79"/>
       <c r="D225" s="22"/>
       <c r="E225" s="22"/>
       <c r="F225" s="73" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="G225" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H225" s="7"/>
       <c r="I225" s="24"/>
@@ -8596,19 +8837,19 @@
     </row>
     <row r="226" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="25" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="B226" s="78" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="C226" s="79"/>
       <c r="D226" s="22"/>
       <c r="E226" s="22"/>
-      <c r="F226" s="29" t="s">
-        <v>572</v>
+      <c r="F226" s="73" t="s">
+        <v>768</v>
       </c>
       <c r="G226" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H226" s="7"/>
       <c r="I226" s="24"/>
@@ -8616,19 +8857,19 @@
     </row>
     <row r="227" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="25" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="B227" s="78" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="C227" s="79"/>
       <c r="D227" s="22"/>
       <c r="E227" s="22"/>
       <c r="F227" s="73" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="G227" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H227" s="7"/>
       <c r="I227" s="24"/>
@@ -8636,19 +8877,19 @@
     </row>
     <row r="228" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="25" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="B228" s="78" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="C228" s="79"/>
       <c r="D228" s="22"/>
       <c r="E228" s="22"/>
-      <c r="F228" s="73" t="s">
-        <v>774</v>
-      </c>
-      <c r="G228" s="23" t="s">
-        <v>261</v>
+      <c r="F228" s="80" t="s">
+        <v>561</v>
+      </c>
+      <c r="G228" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H228" s="7"/>
       <c r="I228" s="24"/>
@@ -8656,19 +8897,19 @@
     </row>
     <row r="229" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="25" t="s">
-        <v>577</v>
+        <v>562</v>
       </c>
       <c r="B229" s="78" t="s">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="C229" s="79"/>
       <c r="D229" s="22"/>
       <c r="E229" s="22"/>
-      <c r="F229" s="73" t="s">
-        <v>775</v>
-      </c>
-      <c r="G229" s="23" t="s">
-        <v>261</v>
+      <c r="F229" s="89" t="s">
+        <v>564</v>
+      </c>
+      <c r="G229" s="73" t="s">
+        <v>260</v>
       </c>
       <c r="H229" s="7"/>
       <c r="I229" s="24"/>
@@ -8676,19 +8917,19 @@
     </row>
     <row r="230" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="25" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="B230" s="78" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="C230" s="79"/>
       <c r="D230" s="22"/>
       <c r="E230" s="22"/>
       <c r="F230" s="73" t="s">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="G230" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H230" s="7"/>
       <c r="I230" s="24"/>
@@ -8696,19 +8937,19 @@
     </row>
     <row r="231" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="25" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="B231" s="78" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="C231" s="79"/>
       <c r="D231" s="22"/>
       <c r="E231" s="22"/>
       <c r="F231" s="73" t="s">
-        <v>749</v>
+        <v>770</v>
       </c>
       <c r="G231" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H231" s="7"/>
       <c r="I231" s="24"/>
@@ -8716,19 +8957,19 @@
     </row>
     <row r="232" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="25" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="B232" s="78" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="C232" s="79"/>
       <c r="D232" s="22"/>
       <c r="E232" s="22"/>
-      <c r="F232" s="73" t="s">
-        <v>735</v>
+      <c r="F232" s="29" t="s">
+        <v>571</v>
       </c>
       <c r="G232" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H232" s="7"/>
       <c r="I232" s="24"/>
@@ -8736,19 +8977,19 @@
     </row>
     <row r="233" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="25" t="s">
-        <v>797</v>
-      </c>
-      <c r="B233" s="190" t="s">
-        <v>798</v>
+        <v>572</v>
+      </c>
+      <c r="B233" s="78" t="s">
+        <v>573</v>
       </c>
       <c r="C233" s="79"/>
       <c r="D233" s="22"/>
       <c r="E233" s="22"/>
-      <c r="F233" s="29" t="s">
-        <v>799</v>
+      <c r="F233" s="73" t="s">
+        <v>732</v>
       </c>
       <c r="G233" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H233" s="7"/>
       <c r="I233" s="24"/>
@@ -8756,19 +8997,19 @@
     </row>
     <row r="234" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="25" t="s">
-        <v>801</v>
+        <v>574</v>
       </c>
       <c r="B234" s="78" t="s">
-        <v>802</v>
+        <v>575</v>
       </c>
       <c r="C234" s="79"/>
       <c r="D234" s="22"/>
       <c r="E234" s="22"/>
-      <c r="F234" s="29" t="s">
-        <v>803</v>
+      <c r="F234" s="73" t="s">
+        <v>771</v>
       </c>
       <c r="G234" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H234" s="7"/>
       <c r="I234" s="24"/>
@@ -8776,112 +9017,160 @@
     </row>
     <row r="235" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="25" t="s">
-        <v>804</v>
+        <v>576</v>
       </c>
       <c r="B235" s="78" t="s">
-        <v>805</v>
+        <v>577</v>
       </c>
       <c r="C235" s="79"/>
       <c r="D235" s="22"/>
       <c r="E235" s="22"/>
-      <c r="F235" s="29" t="s">
-        <v>806</v>
+      <c r="F235" s="73" t="s">
+        <v>772</v>
       </c>
       <c r="G235" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H235" s="7"/>
-      <c r="I235" s="12"/>
-      <c r="J235" s="12"/>
+      <c r="I235" s="24"/>
+      <c r="J235" s="24"/>
     </row>
     <row r="236" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="25" t="s">
-        <v>815</v>
+        <v>578</v>
       </c>
       <c r="B236" s="78" t="s">
-        <v>816</v>
+        <v>579</v>
       </c>
       <c r="C236" s="79"/>
       <c r="D236" s="22"/>
       <c r="E236" s="22"/>
-      <c r="F236" s="29" t="s">
-        <v>817</v>
+      <c r="F236" s="73" t="s">
+        <v>747</v>
       </c>
       <c r="G236" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H236" s="7"/>
-      <c r="I236" s="12"/>
-      <c r="J236" s="12"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="24"/>
     </row>
     <row r="237" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="25"/>
-      <c r="B237" s="78"/>
+      <c r="A237" s="25" t="s">
+        <v>580</v>
+      </c>
+      <c r="B237" s="78" t="s">
+        <v>581</v>
+      </c>
       <c r="C237" s="79"/>
       <c r="D237" s="22"/>
       <c r="E237" s="22"/>
-      <c r="F237" s="29"/>
-      <c r="G237" s="23"/>
+      <c r="F237" s="73" t="s">
+        <v>746</v>
+      </c>
+      <c r="G237" s="23" t="s">
+        <v>260</v>
+      </c>
       <c r="H237" s="7"/>
-      <c r="I237" s="12"/>
-      <c r="J237" s="12"/>
+      <c r="I237" s="24"/>
+      <c r="J237" s="24"/>
     </row>
     <row r="238" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="25"/>
-      <c r="B238" s="78"/>
+      <c r="A238" s="25" t="s">
+        <v>582</v>
+      </c>
+      <c r="B238" s="78" t="s">
+        <v>583</v>
+      </c>
       <c r="C238" s="79"/>
       <c r="D238" s="22"/>
       <c r="E238" s="22"/>
-      <c r="F238" s="29"/>
-      <c r="G238" s="23"/>
+      <c r="F238" s="73" t="s">
+        <v>732</v>
+      </c>
+      <c r="G238" s="23" t="s">
+        <v>260</v>
+      </c>
       <c r="H238" s="7"/>
-      <c r="I238" s="12"/>
-      <c r="J238" s="12"/>
+      <c r="I238" s="24"/>
+      <c r="J238" s="24"/>
     </row>
     <row r="239" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="25"/>
-      <c r="B239" s="78"/>
+      <c r="A239" s="25" t="s">
+        <v>794</v>
+      </c>
+      <c r="B239" s="190" t="s">
+        <v>795</v>
+      </c>
       <c r="C239" s="79"/>
       <c r="D239" s="22"/>
       <c r="E239" s="22"/>
-      <c r="F239" s="29"/>
-      <c r="G239" s="23"/>
+      <c r="F239" s="29" t="s">
+        <v>796</v>
+      </c>
+      <c r="G239" s="23" t="s">
+        <v>260</v>
+      </c>
       <c r="H239" s="7"/>
-      <c r="I239" s="12"/>
-      <c r="J239" s="12"/>
+      <c r="I239" s="24"/>
+      <c r="J239" s="24"/>
     </row>
     <row r="240" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="25"/>
-      <c r="B240" s="78"/>
+      <c r="A240" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="B240" s="78" t="s">
+        <v>799</v>
+      </c>
       <c r="C240" s="79"/>
       <c r="D240" s="22"/>
       <c r="E240" s="22"/>
-      <c r="F240" s="29"/>
-      <c r="G240" s="23"/>
+      <c r="F240" s="29" t="s">
+        <v>800</v>
+      </c>
+      <c r="G240" s="23" t="s">
+        <v>260</v>
+      </c>
       <c r="H240" s="7"/>
-      <c r="I240" s="12"/>
-      <c r="J240" s="12"/>
+      <c r="I240" s="24"/>
+      <c r="J240" s="24"/>
     </row>
     <row r="241" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="25"/>
-      <c r="B241" s="78"/>
+      <c r="A241" s="25" t="s">
+        <v>801</v>
+      </c>
+      <c r="B241" s="78" t="s">
+        <v>802</v>
+      </c>
       <c r="C241" s="79"/>
       <c r="D241" s="22"/>
       <c r="E241" s="22"/>
-      <c r="F241" s="29"/>
-      <c r="G241" s="23"/>
+      <c r="F241" s="29" t="s">
+        <v>803</v>
+      </c>
+      <c r="G241" s="23" t="s">
+        <v>260</v>
+      </c>
       <c r="H241" s="7"/>
       <c r="I241" s="12"/>
       <c r="J241" s="12"/>
     </row>
     <row r="242" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="25"/>
-      <c r="B242" s="78"/>
+      <c r="A242" s="25" t="s">
+        <v>812</v>
+      </c>
+      <c r="B242" s="78" t="s">
+        <v>813</v>
+      </c>
       <c r="C242" s="79"/>
       <c r="D242" s="22"/>
       <c r="E242" s="22"/>
-      <c r="F242" s="29"/>
-      <c r="G242" s="23"/>
+      <c r="F242" s="29" t="s">
+        <v>814</v>
+      </c>
+      <c r="G242" s="23" t="s">
+        <v>260</v>
+      </c>
       <c r="H242" s="7"/>
       <c r="I242" s="12"/>
       <c r="J242" s="12"/>
@@ -8942,7 +9231,7 @@
       <c r="E247" s="22"/>
       <c r="F247" s="29"/>
       <c r="G247" s="23"/>
-      <c r="H247" s="91"/>
+      <c r="H247" s="7"/>
       <c r="I247" s="12"/>
       <c r="J247" s="12"/>
     </row>
@@ -8954,11 +9243,11 @@
       <c r="E248" s="22"/>
       <c r="F248" s="29"/>
       <c r="G248" s="23"/>
-      <c r="H248" s="91"/>
+      <c r="H248" s="7"/>
       <c r="I248" s="12"/>
       <c r="J248" s="12"/>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="25"/>
       <c r="B249" s="78"/>
       <c r="C249" s="79"/>
@@ -8966,7 +9255,9 @@
       <c r="E249" s="22"/>
       <c r="F249" s="29"/>
       <c r="G249" s="23"/>
-      <c r="H249" s="91"/>
+      <c r="H249" s="7"/>
+      <c r="I249" s="12"/>
+      <c r="J249" s="12"/>
     </row>
     <row r="250" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="25"/>
@@ -8976,7 +9267,7 @@
       <c r="E250" s="22"/>
       <c r="F250" s="29"/>
       <c r="G250" s="23"/>
-      <c r="H250" s="91"/>
+      <c r="H250" s="7"/>
       <c r="I250" s="12"/>
       <c r="J250" s="12"/>
     </row>
@@ -8988,7 +9279,7 @@
       <c r="E251" s="22"/>
       <c r="F251" s="29"/>
       <c r="G251" s="23"/>
-      <c r="H251" s="91"/>
+      <c r="H251" s="7"/>
       <c r="I251" s="12"/>
       <c r="J251" s="12"/>
     </row>
@@ -9000,7 +9291,7 @@
       <c r="E252" s="22"/>
       <c r="F252" s="29"/>
       <c r="G252" s="23"/>
-      <c r="H252" s="91"/>
+      <c r="H252" s="7"/>
       <c r="I252" s="12"/>
       <c r="J252" s="12"/>
     </row>
@@ -9028,7 +9319,7 @@
       <c r="I254" s="12"/>
       <c r="J254" s="12"/>
     </row>
-    <row r="255" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="25"/>
       <c r="B255" s="78"/>
       <c r="C255" s="79"/>
@@ -9037,8 +9328,6 @@
       <c r="F255" s="29"/>
       <c r="G255" s="23"/>
       <c r="H255" s="91"/>
-      <c r="I255" s="12"/>
-      <c r="J255" s="12"/>
     </row>
     <row r="256" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="25"/>
@@ -9124,7 +9413,7 @@
       <c r="I262" s="12"/>
       <c r="J262" s="12"/>
     </row>
-    <row r="263" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="25"/>
       <c r="B263" s="78"/>
       <c r="C263" s="79"/>
@@ -9136,7 +9425,7 @@
       <c r="I263" s="12"/>
       <c r="J263" s="12"/>
     </row>
-    <row r="264" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="25"/>
       <c r="B264" s="78"/>
       <c r="C264" s="79"/>
@@ -9148,7 +9437,7 @@
       <c r="I264" s="12"/>
       <c r="J264" s="12"/>
     </row>
-    <row r="265" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="25"/>
       <c r="B265" s="78"/>
       <c r="C265" s="79"/>
@@ -9160,7 +9449,7 @@
       <c r="I265" s="12"/>
       <c r="J265" s="12"/>
     </row>
-    <row r="266" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="25"/>
       <c r="B266" s="78"/>
       <c r="C266" s="79"/>
@@ -9172,7 +9461,7 @@
       <c r="I266" s="12"/>
       <c r="J266" s="12"/>
     </row>
-    <row r="267" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="25"/>
       <c r="B267" s="78"/>
       <c r="C267" s="79"/>
@@ -9184,7 +9473,7 @@
       <c r="I267" s="12"/>
       <c r="J267" s="12"/>
     </row>
-    <row r="268" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="25"/>
       <c r="B268" s="78"/>
       <c r="C268" s="79"/>
@@ -9233,62 +9522,134 @@
       <c r="J271" s="12"/>
     </row>
     <row r="272" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D272" s="11"/>
-      <c r="E272" s="11"/>
+      <c r="A272" s="25"/>
+      <c r="B272" s="78"/>
+      <c r="C272" s="79"/>
+      <c r="D272" s="22"/>
+      <c r="E272" s="22"/>
+      <c r="F272" s="29"/>
+      <c r="G272" s="23"/>
       <c r="H272" s="91"/>
       <c r="I272" s="12"/>
       <c r="J272" s="12"/>
     </row>
-    <row r="273" spans="4:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D273" s="11"/>
-      <c r="E273" s="11"/>
+    <row r="273" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A273" s="25"/>
+      <c r="B273" s="78"/>
+      <c r="C273" s="79"/>
+      <c r="D273" s="22"/>
+      <c r="E273" s="22"/>
+      <c r="F273" s="29"/>
+      <c r="G273" s="23"/>
       <c r="H273" s="91"/>
       <c r="I273" s="12"/>
       <c r="J273" s="12"/>
     </row>
-    <row r="274" spans="4:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D274" s="11"/>
-      <c r="E274" s="11"/>
+    <row r="274" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A274" s="25"/>
+      <c r="B274" s="78"/>
+      <c r="C274" s="79"/>
+      <c r="D274" s="22"/>
+      <c r="E274" s="22"/>
+      <c r="F274" s="29"/>
+      <c r="G274" s="23"/>
       <c r="H274" s="91"/>
       <c r="I274" s="12"/>
       <c r="J274" s="12"/>
     </row>
-    <row r="275" spans="4:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D275" s="11"/>
-      <c r="E275" s="11"/>
+    <row r="275" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A275" s="25"/>
+      <c r="B275" s="78"/>
+      <c r="C275" s="79"/>
+      <c r="D275" s="22"/>
+      <c r="E275" s="22"/>
+      <c r="F275" s="29"/>
+      <c r="G275" s="23"/>
       <c r="H275" s="91"/>
       <c r="I275" s="12"/>
       <c r="J275" s="12"/>
     </row>
-    <row r="276" spans="4:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D276" s="11"/>
-      <c r="E276" s="11"/>
+    <row r="276" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="25"/>
+      <c r="B276" s="78"/>
+      <c r="C276" s="79"/>
+      <c r="D276" s="22"/>
+      <c r="E276" s="22"/>
+      <c r="F276" s="29"/>
+      <c r="G276" s="23"/>
       <c r="H276" s="91"/>
       <c r="I276" s="12"/>
       <c r="J276" s="12"/>
     </row>
-    <row r="277" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="25"/>
+      <c r="B277" s="78"/>
+      <c r="C277" s="79"/>
+      <c r="D277" s="22"/>
+      <c r="E277" s="22"/>
+      <c r="F277" s="29"/>
+      <c r="G277" s="23"/>
       <c r="H277" s="91"/>
-    </row>
-    <row r="278" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="I277" s="12"/>
+      <c r="J277" s="12"/>
+    </row>
+    <row r="278" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D278" s="11"/>
+      <c r="E278" s="11"/>
       <c r="H278" s="91"/>
-    </row>
-    <row r="279" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="I278" s="12"/>
+      <c r="J278" s="12"/>
+    </row>
+    <row r="279" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D279" s="11"/>
+      <c r="E279" s="11"/>
       <c r="H279" s="91"/>
-    </row>
-    <row r="280" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="I279" s="12"/>
+      <c r="J279" s="12"/>
+    </row>
+    <row r="280" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D280" s="11"/>
+      <c r="E280" s="11"/>
       <c r="H280" s="91"/>
-    </row>
-    <row r="281" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="I280" s="12"/>
+      <c r="J280" s="12"/>
+    </row>
+    <row r="281" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D281" s="11"/>
+      <c r="E281" s="11"/>
       <c r="H281" s="91"/>
-    </row>
-    <row r="282" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="I281" s="12"/>
+      <c r="J281" s="12"/>
+    </row>
+    <row r="282" spans="1:10" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D282" s="11"/>
+      <c r="E282" s="11"/>
       <c r="H282" s="91"/>
+      <c r="I282" s="12"/>
+      <c r="J282" s="12"/>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H283" s="91"/>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H284" s="91"/>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H285" s="91"/>
+    </row>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H286" s="91"/>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H287" s="91"/>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H288" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A92:F92"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.78749999999999998" bottom="0.59097222222222201" header="0.31527777777777799" footer="0.31527777777777799"/>
@@ -9337,67 +9698,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="216" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="191"/>
-      <c r="C1" s="191"/>
+      <c r="B1" s="216"/>
+      <c r="C1" s="216"/>
       <c r="D1" s="93"/>
       <c r="E1" s="94"/>
       <c r="F1" s="94"/>
       <c r="G1" s="95"/>
       <c r="H1" s="96"/>
       <c r="T1" s="9"/>
-      <c r="U1" s="193" t="s">
+      <c r="U1" s="218" t="s">
+        <v>584</v>
+      </c>
+      <c r="V1" s="219" t="s">
         <v>585</v>
       </c>
-      <c r="V1" s="194" t="s">
-        <v>586</v>
-      </c>
-      <c r="W1" s="194"/>
-      <c r="X1" s="194"/>
-      <c r="Y1" s="194"/>
+      <c r="W1" s="219"/>
+      <c r="X1" s="219"/>
+      <c r="Y1" s="219"/>
       <c r="Z1" s="9"/>
       <c r="AA1" s="97"/>
     </row>
     <row r="2" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="B2" s="98" t="s">
+      <c r="C2" s="99" t="s">
+        <v>586</v>
+      </c>
+      <c r="D2" s="100" t="s">
+        <v>587</v>
+      </c>
+      <c r="E2" s="100" t="s">
         <v>250</v>
       </c>
-      <c r="C2" s="99" t="s">
+      <c r="F2" s="100" t="s">
         <v>587</v>
-      </c>
-      <c r="D2" s="100" t="s">
-        <v>588</v>
-      </c>
-      <c r="E2" s="100" t="s">
-        <v>251</v>
-      </c>
-      <c r="F2" s="100" t="s">
-        <v>588</v>
       </c>
       <c r="G2" s="85"/>
       <c r="H2" s="96"/>
       <c r="T2" s="9"/>
-      <c r="U2" s="193"/>
+      <c r="U2" s="218"/>
       <c r="V2" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="W2" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="X2" s="101" t="s">
         <v>589</v>
       </c>
-      <c r="X2" s="101" t="s">
+      <c r="Y2" s="97" t="s">
         <v>590</v>
-      </c>
-      <c r="Y2" s="97" t="s">
-        <v>591</v>
       </c>
       <c r="Z2" s="9"/>
       <c r="AA2" s="101" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -9417,14 +9778,14 @@
       <c r="F3" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="195" t="s">
+      <c r="G3" s="220" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="195"/>
-      <c r="I3" s="195"/>
+      <c r="H3" s="220"/>
+      <c r="I3" s="220"/>
       <c r="T3" s="96"/>
       <c r="V3" s="11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="W3" s="11">
         <v>33</v>
@@ -9472,10 +9833,10 @@
       <c r="H5" s="96"/>
       <c r="T5" s="96"/>
       <c r="U5" s="106" t="s">
+        <v>593</v>
+      </c>
+      <c r="V5" s="11" t="s">
         <v>594</v>
-      </c>
-      <c r="V5" s="11" t="s">
-        <v>595</v>
       </c>
       <c r="W5" s="11">
         <v>-4143</v>
@@ -9508,10 +9869,10 @@
       </c>
       <c r="T6" s="96"/>
       <c r="U6" s="106" t="s">
+        <v>595</v>
+      </c>
+      <c r="V6" s="11" t="s">
         <v>596</v>
-      </c>
-      <c r="V6" s="11" t="s">
-        <v>597</v>
       </c>
       <c r="W6" s="11">
         <v>62</v>
@@ -9545,10 +9906,10 @@
       <c r="H7" s="96"/>
       <c r="T7" s="96"/>
       <c r="U7" s="106" t="s">
+        <v>595</v>
+      </c>
+      <c r="V7" s="11" t="s">
         <v>596</v>
-      </c>
-      <c r="V7" s="11" t="s">
-        <v>597</v>
       </c>
       <c r="W7" s="11">
         <v>-62</v>
@@ -9579,9 +9940,9 @@
       <c r="F8" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="196"/>
-      <c r="H8" s="196"/>
-      <c r="I8" s="196"/>
+      <c r="G8" s="221"/>
+      <c r="H8" s="221"/>
+      <c r="I8" s="221"/>
       <c r="T8" s="96"/>
       <c r="U8" s="106"/>
       <c r="Y8" s="92">
@@ -9627,7 +9988,7 @@
         <v>41</v>
       </c>
       <c r="D10" s="105" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E10" s="80" t="s">
         <v>42</v>
@@ -9635,9 +9996,9 @@
       <c r="F10" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="196"/>
-      <c r="H10" s="196"/>
-      <c r="I10" s="196"/>
+      <c r="G10" s="221"/>
+      <c r="H10" s="221"/>
+      <c r="I10" s="221"/>
       <c r="T10" s="96"/>
       <c r="U10" s="106"/>
       <c r="Y10" s="92">
@@ -9709,7 +10070,7 @@
         <v>41</v>
       </c>
       <c r="D13" s="105" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E13" s="80" t="s">
         <v>52</v>
@@ -9734,7 +10095,7 @@
       <c r="C14" s="27"/>
       <c r="D14" s="105"/>
       <c r="E14" s="80" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F14" s="80"/>
       <c r="H14" s="96"/>
@@ -9785,11 +10146,11 @@
       <c r="F16" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="197" t="s">
+      <c r="G16" s="222" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="197"/>
-      <c r="I16" s="197"/>
+      <c r="H16" s="222"/>
+      <c r="I16" s="222"/>
       <c r="T16" s="96"/>
       <c r="U16" s="106"/>
       <c r="Y16" s="92">
@@ -9809,7 +10170,7 @@
         <v>66</v>
       </c>
       <c r="D17" s="108" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E17" s="80" t="s">
         <v>67</v>
@@ -9837,7 +10198,7 @@
         <v>66</v>
       </c>
       <c r="D18" s="108" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E18" s="80" t="s">
         <v>70</v>
@@ -9981,11 +10342,11 @@
       <c r="F24" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="198" t="s">
+      <c r="G24" s="223" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="198"/>
-      <c r="I24" s="198"/>
+      <c r="H24" s="223"/>
+      <c r="I24" s="223"/>
       <c r="T24" s="96"/>
       <c r="U24" s="106"/>
       <c r="Y24" s="92">
@@ -10079,7 +10440,7 @@
         <v>27</v>
       </c>
       <c r="D28" s="105" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E28" s="80" t="s">
         <v>106</v>
@@ -10087,11 +10448,11 @@
       <c r="F28" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="G28" s="195" t="s">
+      <c r="G28" s="220" t="s">
         <v>16</v>
       </c>
-      <c r="H28" s="195"/>
-      <c r="I28" s="195"/>
+      <c r="H28" s="220"/>
+      <c r="I28" s="220"/>
       <c r="J28" s="92"/>
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
@@ -10120,7 +10481,7 @@
         <v>27</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E29" s="80" t="s">
         <v>109</v>
@@ -10174,11 +10535,11 @@
       <c r="F31" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="G31" s="199" t="s">
+      <c r="G31" s="224" t="s">
         <v>117</v>
       </c>
-      <c r="H31" s="199"/>
-      <c r="I31" s="199"/>
+      <c r="H31" s="224"/>
+      <c r="I31" s="224"/>
       <c r="T31" s="96"/>
       <c r="Y31" s="92">
         <f t="shared" si="2"/>
@@ -10188,15 +10549,15 @@
     </row>
     <row r="32" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
+        <v>599</v>
+      </c>
+      <c r="B32" s="43" t="s">
         <v>600</v>
-      </c>
-      <c r="B32" s="43" t="s">
-        <v>601</v>
       </c>
       <c r="C32" s="44"/>
       <c r="D32" s="42"/>
       <c r="E32" s="80" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F32" s="80"/>
       <c r="H32" s="96"/>
@@ -10271,11 +10632,11 @@
       <c r="D35" s="112"/>
       <c r="E35" s="80"/>
       <c r="F35" s="80"/>
-      <c r="G35" s="204" t="s">
+      <c r="G35" s="229" t="s">
         <v>137</v>
       </c>
-      <c r="H35" s="204"/>
-      <c r="I35" s="204"/>
+      <c r="H35" s="229"/>
+      <c r="I35" s="229"/>
       <c r="T35" s="96"/>
       <c r="U35" s="106"/>
       <c r="Y35" s="92"/>
@@ -10328,11 +10689,11 @@
         <v>163</v>
       </c>
       <c r="F38" s="80"/>
-      <c r="G38" s="205" t="s">
+      <c r="G38" s="230" t="s">
         <v>164</v>
       </c>
-      <c r="H38" s="205"/>
-      <c r="I38" s="205"/>
+      <c r="H38" s="230"/>
+      <c r="I38" s="230"/>
       <c r="T38" s="96"/>
       <c r="U38" s="106"/>
       <c r="Y38" s="92">
@@ -10374,7 +10735,7 @@
         <v>170</v>
       </c>
       <c r="D40" s="112" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E40" s="80" t="s">
         <v>171</v>
@@ -10382,11 +10743,11 @@
       <c r="F40" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="G40" s="204" t="s">
+      <c r="G40" s="229" t="s">
         <v>137</v>
       </c>
-      <c r="H40" s="204"/>
-      <c r="I40" s="204"/>
+      <c r="H40" s="229"/>
+      <c r="I40" s="229"/>
       <c r="J40" s="92"/>
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
@@ -10410,7 +10771,7 @@
         <v>170</v>
       </c>
       <c r="D41" s="112" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E41" s="80" t="s">
         <v>174</v>
@@ -10435,7 +10796,7 @@
         <v>170</v>
       </c>
       <c r="D42" s="112" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E42" s="80" t="s">
         <v>177</v>
@@ -10476,7 +10837,7 @@
       </c>
       <c r="C44" s="49"/>
       <c r="D44" s="112" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E44" s="80"/>
       <c r="F44" s="80"/>
@@ -10495,7 +10856,7 @@
       </c>
       <c r="C45" s="49"/>
       <c r="D45" s="112" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E45" s="80"/>
       <c r="F45" s="80"/>
@@ -10516,7 +10877,7 @@
         <v>170</v>
       </c>
       <c r="D46" s="112" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E46" s="80" t="s">
         <v>191</v>
@@ -10676,11 +11037,11 @@
       <c r="F54" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="G54" s="200" t="s">
+      <c r="G54" s="225" t="s">
         <v>214</v>
       </c>
-      <c r="H54" s="200"/>
-      <c r="I54" s="200"/>
+      <c r="H54" s="225"/>
+      <c r="I54" s="225"/>
       <c r="T54" s="96"/>
       <c r="U54" s="106"/>
       <c r="Y54" s="92">
@@ -10700,7 +11061,7 @@
         <v>66</v>
       </c>
       <c r="D55" s="105" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E55" s="80" t="s">
         <v>217</v>
@@ -10750,7 +11111,7 @@
         <v>66</v>
       </c>
       <c r="D57" s="116" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E57" s="80" t="s">
         <v>223</v>
@@ -10876,11 +11237,11 @@
         <v>242</v>
       </c>
       <c r="C63" s="59" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D63" s="117"/>
       <c r="E63" s="89" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F63" s="104" t="s">
         <v>15</v>
@@ -10946,13 +11307,13 @@
       <c r="Y67" s="92"/>
     </row>
     <row r="68" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="206" t="s">
-        <v>248</v>
-      </c>
-      <c r="B68" s="206"/>
-      <c r="C68" s="206"/>
-      <c r="D68" s="206"/>
-      <c r="E68" s="206"/>
+      <c r="A68" s="231" t="s">
+        <v>247</v>
+      </c>
+      <c r="B68" s="231"/>
+      <c r="C68" s="231"/>
+      <c r="D68" s="231"/>
+      <c r="E68" s="231"/>
       <c r="F68" s="64"/>
       <c r="G68" s="122"/>
       <c r="H68" s="96"/>
@@ -10965,15 +11326,15 @@
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" s="123" t="s">
+        <v>248</v>
+      </c>
+      <c r="B69" s="99" t="s">
         <v>249</v>
-      </c>
-      <c r="B69" s="99" t="s">
-        <v>250</v>
       </c>
       <c r="C69" s="99"/>
       <c r="D69" s="99"/>
       <c r="E69" s="99" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F69" s="99"/>
       <c r="G69" s="85"/>
@@ -10983,22 +11344,22 @@
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" s="124" t="s">
+        <v>251</v>
+      </c>
+      <c r="B70" s="71" t="s">
         <v>252</v>
-      </c>
-      <c r="B70" s="71" t="s">
-        <v>253</v>
       </c>
       <c r="C70" s="71"/>
       <c r="D70" s="71"/>
       <c r="E70" s="73" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F70" s="73"/>
-      <c r="G70" s="200" t="s">
+      <c r="G70" s="225" t="s">
         <v>214</v>
       </c>
-      <c r="H70" s="200"/>
-      <c r="I70" s="200"/>
+      <c r="H70" s="225"/>
+      <c r="I70" s="225"/>
       <c r="S70" s="92"/>
       <c r="Y70" s="92">
         <f>SUM(W70*X70)</f>
@@ -11007,24 +11368,24 @@
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="B71" s="78" t="s">
         <v>266</v>
-      </c>
-      <c r="B71" s="78" t="s">
-        <v>267</v>
       </c>
       <c r="C71" s="78"/>
       <c r="D71" s="78"/>
       <c r="E71" s="80" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F71" s="80" t="s">
         <v>129</v>
       </c>
-      <c r="G71" s="201" t="s">
-        <v>605</v>
-      </c>
-      <c r="H71" s="201"/>
-      <c r="I71" s="201"/>
+      <c r="G71" s="226" t="s">
+        <v>604</v>
+      </c>
+      <c r="H71" s="226"/>
+      <c r="I71" s="226"/>
       <c r="S71" s="92"/>
       <c r="Y71" s="125">
         <f>SUM(Y74)</f>
@@ -11033,18 +11394,18 @@
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
+        <v>292</v>
+      </c>
+      <c r="B72" s="78" t="s">
         <v>293</v>
-      </c>
-      <c r="B72" s="78" t="s">
-        <v>294</v>
       </c>
       <c r="C72" s="78"/>
       <c r="D72" s="78"/>
       <c r="E72" s="80" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F72" s="80" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H72" s="96"/>
       <c r="S72" s="92"/>
@@ -11052,13 +11413,13 @@
     </row>
     <row r="73" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="28" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B73" s="78"/>
       <c r="C73" s="78"/>
       <c r="D73" s="78"/>
       <c r="E73" s="80" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F73" s="80" t="s">
         <v>129</v>
@@ -11072,13 +11433,13 @@
     </row>
     <row r="74" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="28" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B74" s="78"/>
       <c r="C74" s="78"/>
       <c r="D74" s="78"/>
       <c r="E74" s="80" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F74" s="80" t="s">
         <v>129</v>
@@ -11094,13 +11455,13 @@
     </row>
     <row r="75" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="28" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B75" s="78"/>
       <c r="C75" s="78"/>
       <c r="D75" s="78"/>
       <c r="E75" s="80" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F75" s="80" t="s">
         <v>129</v>
@@ -11111,13 +11472,13 @@
     </row>
     <row r="76" spans="1:27" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B76" s="78"/>
       <c r="C76" s="78"/>
       <c r="D76" s="78"/>
       <c r="E76" s="80" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F76" s="80" t="s">
         <v>129</v>
@@ -11134,13 +11495,13 @@
     </row>
     <row r="77" spans="1:27" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="28" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B77" s="78"/>
       <c r="C77" s="78"/>
       <c r="D77" s="78"/>
       <c r="E77" s="80" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F77" s="80" t="s">
         <v>129</v>
@@ -11157,13 +11518,13 @@
     </row>
     <row r="78" spans="1:27" s="11" customFormat="1" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="28" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B78" s="78"/>
       <c r="C78" s="78"/>
       <c r="D78" s="78"/>
       <c r="E78" s="80" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F78" s="80" t="s">
         <v>129</v>
@@ -11180,13 +11541,13 @@
     </row>
     <row r="79" spans="1:27" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="28" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B79" s="78"/>
       <c r="C79" s="78"/>
       <c r="D79" s="78"/>
       <c r="E79" s="80" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F79" s="80" t="s">
         <v>129</v>
@@ -11203,15 +11564,15 @@
     </row>
     <row r="80" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="B80" s="78" t="s">
         <v>336</v>
-      </c>
-      <c r="B80" s="78" t="s">
-        <v>337</v>
       </c>
       <c r="C80" s="78"/>
       <c r="D80" s="78"/>
       <c r="E80" s="80" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F80" s="80" t="s">
         <v>129</v>
@@ -11228,18 +11589,18 @@
     </row>
     <row r="81" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="B81" s="78" t="s">
         <v>341</v>
-      </c>
-      <c r="B81" s="78" t="s">
-        <v>342</v>
       </c>
       <c r="C81" s="78"/>
       <c r="D81" s="78"/>
       <c r="E81" s="80" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F81" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G81" s="92"/>
       <c r="H81" s="96"/>
@@ -11253,16 +11614,16 @@
     </row>
     <row r="82" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="B82" s="78" t="s">
         <v>344</v>
-      </c>
-      <c r="B82" s="78" t="s">
-        <v>345</v>
       </c>
       <c r="C82" s="78"/>
       <c r="D82" s="78"/>
       <c r="E82" s="80"/>
       <c r="F82" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G82" s="92"/>
       <c r="H82" s="96"/>
@@ -11276,15 +11637,15 @@
     </row>
     <row r="83" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="B83" s="78" t="s">
         <v>347</v>
-      </c>
-      <c r="B83" s="78" t="s">
-        <v>348</v>
       </c>
       <c r="C83" s="78"/>
       <c r="D83" s="78"/>
       <c r="E83" s="80" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F83" s="80" t="s">
         <v>129</v>
@@ -11301,16 +11662,16 @@
     </row>
     <row r="84" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="B84" s="78" t="s">
         <v>350</v>
-      </c>
-      <c r="B84" s="78" t="s">
-        <v>351</v>
       </c>
       <c r="C84" s="78"/>
       <c r="D84" s="78"/>
       <c r="E84" s="80"/>
       <c r="F84" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G84" s="92"/>
       <c r="H84" s="96"/>
@@ -11324,18 +11685,18 @@
     </row>
     <row r="85" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="28" t="s">
+        <v>351</v>
+      </c>
+      <c r="B85" s="78" t="s">
         <v>352</v>
-      </c>
-      <c r="B85" s="78" t="s">
-        <v>353</v>
       </c>
       <c r="C85" s="78"/>
       <c r="D85" s="78"/>
       <c r="E85" s="80" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F85" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G85" s="92"/>
       <c r="H85" s="96"/>
@@ -11349,18 +11710,18 @@
     </row>
     <row r="86" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="28" t="s">
+        <v>354</v>
+      </c>
+      <c r="B86" s="78" t="s">
         <v>355</v>
-      </c>
-      <c r="B86" s="78" t="s">
-        <v>356</v>
       </c>
       <c r="C86" s="78"/>
       <c r="D86" s="78"/>
       <c r="E86" s="80" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F86" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G86" s="92"/>
       <c r="H86" s="96"/>
@@ -11374,15 +11735,15 @@
     </row>
     <row r="87" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="B87" s="78" t="s">
         <v>358</v>
-      </c>
-      <c r="B87" s="78" t="s">
-        <v>359</v>
       </c>
       <c r="C87" s="78"/>
       <c r="D87" s="78"/>
       <c r="E87" s="80" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F87" s="80" t="s">
         <v>129</v>
@@ -11399,15 +11760,15 @@
     </row>
     <row r="88" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="28" t="s">
+        <v>368</v>
+      </c>
+      <c r="B88" s="78" t="s">
         <v>369</v>
-      </c>
-      <c r="B88" s="78" t="s">
-        <v>370</v>
       </c>
       <c r="C88" s="78"/>
       <c r="D88" s="78"/>
       <c r="E88" s="80" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F88" s="80" t="s">
         <v>129</v>
@@ -11424,15 +11785,15 @@
     </row>
     <row r="89" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="28" t="s">
+        <v>371</v>
+      </c>
+      <c r="B89" s="78" t="s">
         <v>372</v>
-      </c>
-      <c r="B89" s="78" t="s">
-        <v>373</v>
       </c>
       <c r="C89" s="78"/>
       <c r="D89" s="78"/>
       <c r="E89" s="80" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F89" s="80" t="s">
         <v>129</v>
@@ -11449,15 +11810,15 @@
     </row>
     <row r="90" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="28" t="s">
+        <v>374</v>
+      </c>
+      <c r="B90" s="78" t="s">
         <v>375</v>
-      </c>
-      <c r="B90" s="78" t="s">
-        <v>376</v>
       </c>
       <c r="C90" s="78"/>
       <c r="D90" s="78"/>
       <c r="E90" s="80" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F90" s="80" t="s">
         <v>129</v>
@@ -11474,15 +11835,15 @@
     </row>
     <row r="91" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="28" t="s">
+        <v>377</v>
+      </c>
+      <c r="B91" s="78" t="s">
         <v>378</v>
-      </c>
-      <c r="B91" s="78" t="s">
-        <v>379</v>
       </c>
       <c r="C91" s="78"/>
       <c r="D91" s="78"/>
       <c r="E91" s="80" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F91" s="80" t="s">
         <v>129</v>
@@ -11499,15 +11860,15 @@
     </row>
     <row r="92" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="B92" s="78" t="s">
         <v>381</v>
-      </c>
-      <c r="B92" s="78" t="s">
-        <v>382</v>
       </c>
       <c r="C92" s="78"/>
       <c r="D92" s="78"/>
       <c r="E92" s="80" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F92" s="80" t="s">
         <v>129</v>
@@ -11524,15 +11885,15 @@
     </row>
     <row r="93" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="28" t="s">
+        <v>388</v>
+      </c>
+      <c r="B93" s="78" t="s">
         <v>389</v>
-      </c>
-      <c r="B93" s="78" t="s">
-        <v>390</v>
       </c>
       <c r="C93" s="78"/>
       <c r="D93" s="78"/>
       <c r="E93" s="80" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F93" s="80" t="s">
         <v>129</v>
@@ -11548,13 +11909,13 @@
     </row>
     <row r="94" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="28" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B94" s="78"/>
       <c r="C94" s="78"/>
       <c r="D94" s="78"/>
       <c r="E94" s="80" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F94" s="80" t="s">
         <v>129</v>
@@ -11563,15 +11924,15 @@
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A95" s="28" t="s">
+        <v>394</v>
+      </c>
+      <c r="B95" s="78" t="s">
         <v>395</v>
-      </c>
-      <c r="B95" s="78" t="s">
-        <v>396</v>
       </c>
       <c r="C95" s="78"/>
       <c r="D95" s="78"/>
       <c r="E95" s="80" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F95" s="80" t="s">
         <v>129</v>
@@ -11580,15 +11941,15 @@
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A96" s="28" t="s">
+        <v>397</v>
+      </c>
+      <c r="B96" s="78" t="s">
         <v>398</v>
-      </c>
-      <c r="B96" s="78" t="s">
-        <v>399</v>
       </c>
       <c r="C96" s="78"/>
       <c r="D96" s="78"/>
       <c r="E96" s="80" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F96" s="80" t="s">
         <v>129</v>
@@ -11597,15 +11958,15 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="28" t="s">
+        <v>400</v>
+      </c>
+      <c r="B97" s="78" t="s">
         <v>401</v>
-      </c>
-      <c r="B97" s="78" t="s">
-        <v>402</v>
       </c>
       <c r="C97" s="78"/>
       <c r="D97" s="78"/>
       <c r="E97" s="80" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F97" s="73" t="s">
         <v>15</v>
@@ -11614,15 +11975,15 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="28" t="s">
+        <v>402</v>
+      </c>
+      <c r="B98" s="78" t="s">
         <v>403</v>
-      </c>
-      <c r="B98" s="78" t="s">
-        <v>404</v>
       </c>
       <c r="C98" s="78"/>
       <c r="D98" s="78"/>
       <c r="E98" s="80" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F98" s="80" t="s">
         <v>129</v>
@@ -11631,15 +11992,15 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="28" t="s">
+        <v>405</v>
+      </c>
+      <c r="B99" s="78" t="s">
         <v>406</v>
-      </c>
-      <c r="B99" s="78" t="s">
-        <v>407</v>
       </c>
       <c r="C99" s="78"/>
       <c r="D99" s="78"/>
       <c r="E99" s="80" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F99" s="80" t="s">
         <v>129</v>
@@ -11648,15 +12009,15 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="28" t="s">
+        <v>422</v>
+      </c>
+      <c r="B100" s="78" t="s">
         <v>423</v>
-      </c>
-      <c r="B100" s="78" t="s">
-        <v>424</v>
       </c>
       <c r="C100" s="78"/>
       <c r="D100" s="78"/>
       <c r="E100" s="80" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F100" s="80" t="s">
         <v>129</v>
@@ -11665,117 +12026,117 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="28" t="s">
+        <v>429</v>
+      </c>
+      <c r="B101" s="78" t="s">
         <v>430</v>
-      </c>
-      <c r="B101" s="78" t="s">
-        <v>431</v>
       </c>
       <c r="C101" s="78"/>
       <c r="D101" s="78"/>
       <c r="E101" s="80" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F101" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H101" s="96"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="B102" s="78" t="s">
         <v>433</v>
-      </c>
-      <c r="B102" s="78" t="s">
-        <v>434</v>
       </c>
       <c r="C102" s="78"/>
       <c r="D102" s="78"/>
       <c r="E102" s="80" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F102" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H102" s="96"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="B103" s="78" t="s">
         <v>442</v>
-      </c>
-      <c r="B103" s="78" t="s">
-        <v>443</v>
       </c>
       <c r="C103" s="78"/>
       <c r="D103" s="78"/>
       <c r="E103" s="86" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F103" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H103" s="96"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="28" t="s">
+        <v>448</v>
+      </c>
+      <c r="B104" s="78" t="s">
         <v>449</v>
-      </c>
-      <c r="B104" s="78" t="s">
-        <v>450</v>
       </c>
       <c r="C104" s="78"/>
       <c r="D104" s="78"/>
       <c r="E104" s="80" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F104" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H104" s="96"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="28" t="s">
+        <v>459</v>
+      </c>
+      <c r="B105" s="78" t="s">
         <v>460</v>
-      </c>
-      <c r="B105" s="78" t="s">
-        <v>461</v>
       </c>
       <c r="C105" s="78"/>
       <c r="D105" s="78"/>
       <c r="E105" s="80" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F105" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H105" s="96"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="28" t="s">
+        <v>462</v>
+      </c>
+      <c r="B106" s="78" t="s">
         <v>463</v>
-      </c>
-      <c r="B106" s="78" t="s">
-        <v>464</v>
       </c>
       <c r="C106" s="78"/>
       <c r="D106" s="78"/>
       <c r="E106" s="80" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F106" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H106" s="96"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="28" t="s">
+        <v>465</v>
+      </c>
+      <c r="B107" s="78" t="s">
         <v>466</v>
-      </c>
-      <c r="B107" s="78" t="s">
-        <v>467</v>
       </c>
       <c r="C107" s="78"/>
       <c r="D107" s="78"/>
       <c r="E107" s="80" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F107" s="80" t="s">
         <v>129</v>
@@ -11784,15 +12145,15 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="28" t="s">
+        <v>470</v>
+      </c>
+      <c r="B108" s="78" t="s">
         <v>471</v>
-      </c>
-      <c r="B108" s="78" t="s">
-        <v>472</v>
       </c>
       <c r="C108" s="78"/>
       <c r="D108" s="78"/>
       <c r="E108" s="80" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F108" s="80" t="s">
         <v>129</v>
@@ -11801,126 +12162,126 @@
     </row>
     <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="28" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B109" s="78"/>
       <c r="C109" s="78"/>
       <c r="D109" s="78"/>
       <c r="E109" s="80" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F109" s="73"/>
       <c r="H109" s="96"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="B110" s="78" t="s">
         <v>485</v>
-      </c>
-      <c r="B110" s="78" t="s">
-        <v>486</v>
       </c>
       <c r="C110" s="78"/>
       <c r="D110" s="78"/>
       <c r="E110" s="80" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F110" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H110" s="96"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="28" t="s">
+        <v>487</v>
+      </c>
+      <c r="B111" s="78" t="s">
         <v>488</v>
-      </c>
-      <c r="B111" s="78" t="s">
-        <v>489</v>
       </c>
       <c r="C111" s="78"/>
       <c r="D111" s="78"/>
       <c r="E111" s="80" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F111" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H111" s="96"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="28" t="s">
+        <v>490</v>
+      </c>
+      <c r="B112" s="78" t="s">
         <v>491</v>
-      </c>
-      <c r="B112" s="78" t="s">
-        <v>492</v>
       </c>
       <c r="C112" s="78"/>
       <c r="D112" s="78"/>
       <c r="E112" s="80" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F112" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H112" s="96"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="28" t="s">
+        <v>508</v>
+      </c>
+      <c r="B113" s="78" t="s">
         <v>509</v>
-      </c>
-      <c r="B113" s="78" t="s">
-        <v>510</v>
       </c>
       <c r="C113" s="78"/>
       <c r="D113" s="78"/>
       <c r="E113" s="80" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F113" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H113" s="96"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="B114" s="78" t="s">
         <v>514</v>
-      </c>
-      <c r="B114" s="78" t="s">
-        <v>515</v>
       </c>
       <c r="C114" s="78"/>
       <c r="D114" s="78"/>
       <c r="E114" s="80" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F114" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H114" s="96"/>
     </row>
     <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="28" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B115" s="78"/>
       <c r="C115" s="78"/>
       <c r="D115" s="78"/>
       <c r="E115" s="80" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F115" s="73"/>
       <c r="H115" s="96"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="28" t="s">
+        <v>520</v>
+      </c>
+      <c r="B116" s="78" t="s">
         <v>521</v>
-      </c>
-      <c r="B116" s="78" t="s">
-        <v>522</v>
       </c>
       <c r="C116" s="78"/>
       <c r="D116" s="78"/>
       <c r="E116" s="80" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F116" s="80" t="s">
         <v>129</v>
@@ -11929,49 +12290,49 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="28" t="s">
+        <v>527</v>
+      </c>
+      <c r="B117" s="78" t="s">
         <v>528</v>
-      </c>
-      <c r="B117" s="78" t="s">
-        <v>529</v>
       </c>
       <c r="C117" s="78"/>
       <c r="D117" s="78"/>
       <c r="E117" s="80" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F117" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H117" s="96"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="28" t="s">
+        <v>530</v>
+      </c>
+      <c r="B118" s="78" t="s">
         <v>531</v>
-      </c>
-      <c r="B118" s="78" t="s">
-        <v>532</v>
       </c>
       <c r="C118" s="78"/>
       <c r="D118" s="78"/>
       <c r="E118" s="80" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F118" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H118" s="96"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="28" t="s">
+        <v>533</v>
+      </c>
+      <c r="B119" s="78" t="s">
         <v>534</v>
-      </c>
-      <c r="B119" s="78" t="s">
-        <v>535</v>
       </c>
       <c r="C119" s="78"/>
       <c r="D119" s="78"/>
       <c r="E119" s="80" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F119" s="80" t="s">
         <v>129</v>
@@ -11980,80 +12341,80 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="28" t="s">
+        <v>536</v>
+      </c>
+      <c r="B120" s="78" t="s">
         <v>537</v>
-      </c>
-      <c r="B120" s="78" t="s">
-        <v>538</v>
       </c>
       <c r="C120" s="78"/>
       <c r="D120" s="78"/>
       <c r="E120" s="80" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F120" s="73"/>
       <c r="H120" s="96"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="28" t="s">
+        <v>559</v>
+      </c>
+      <c r="B121" s="78" t="s">
         <v>560</v>
-      </c>
-      <c r="B121" s="78" t="s">
-        <v>561</v>
       </c>
       <c r="C121" s="78"/>
       <c r="D121" s="78"/>
       <c r="E121" s="80" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F121" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H121" s="96"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="45" t="s">
+        <v>562</v>
+      </c>
+      <c r="B122" s="129" t="s">
         <v>563</v>
-      </c>
-      <c r="B122" s="129" t="s">
-        <v>564</v>
       </c>
       <c r="C122" s="129"/>
       <c r="D122" s="129"/>
       <c r="E122" s="89" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F122" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H122" s="96"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="B123" s="129" t="s">
         <v>255</v>
-      </c>
-      <c r="B123" s="129" t="s">
-        <v>256</v>
       </c>
       <c r="C123" s="129"/>
       <c r="D123" s="129"/>
       <c r="E123" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F123" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="G123" s="202" t="s">
-        <v>258</v>
-      </c>
-      <c r="H123" s="202"/>
-      <c r="I123" s="202"/>
+      <c r="G123" s="227" t="s">
+        <v>257</v>
+      </c>
+      <c r="H123" s="227"/>
+      <c r="I123" s="227"/>
     </row>
     <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="25" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C124" s="10"/>
       <c r="D124" s="10"/>
@@ -12078,7 +12439,7 @@
     </row>
     <row r="127" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A127" s="131" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B127" s="132"/>
       <c r="C127" s="88"/>
@@ -12325,84 +12686,84 @@
       <c r="H178" s="96"/>
     </row>
     <row r="180" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A180" s="203" t="s">
-        <v>613</v>
-      </c>
-      <c r="B180" s="203"/>
-      <c r="C180" s="203"/>
-      <c r="D180" s="203"/>
-      <c r="E180" s="203"/>
+      <c r="A180" s="228" t="s">
+        <v>612</v>
+      </c>
+      <c r="B180" s="228"/>
+      <c r="C180" s="228"/>
+      <c r="D180" s="228"/>
+      <c r="E180" s="228"/>
       <c r="F180" s="135"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="136" t="s">
+        <v>248</v>
+      </c>
+      <c r="B181" s="99" t="s">
         <v>249</v>
-      </c>
-      <c r="B181" s="99" t="s">
-        <v>250</v>
       </c>
       <c r="C181" s="99"/>
       <c r="D181" s="99"/>
       <c r="E181" s="99" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F181" s="99" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="28" t="s">
+        <v>613</v>
+      </c>
+      <c r="E182" s="90" t="s">
         <v>614</v>
       </c>
-      <c r="E182" s="90" t="s">
-        <v>615</v>
-      </c>
       <c r="F182" s="90" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="28" t="s">
+        <v>615</v>
+      </c>
+      <c r="E183" s="137" t="s">
         <v>616</v>
       </c>
-      <c r="E183" s="137" t="s">
-        <v>617</v>
-      </c>
       <c r="F183" s="137" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="28" t="s">
+        <v>617</v>
+      </c>
+      <c r="E184" s="90" t="s">
         <v>618</v>
       </c>
-      <c r="E184" s="90" t="s">
-        <v>619</v>
-      </c>
       <c r="F184" s="90" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="28" t="s">
+        <v>619</v>
+      </c>
+      <c r="E185" s="90" t="s">
         <v>620</v>
       </c>
-      <c r="E185" s="90" t="s">
-        <v>621</v>
-      </c>
       <c r="F185" s="90" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="28" t="s">
+        <v>621</v>
+      </c>
+      <c r="E186" s="90" t="s">
         <v>622</v>
       </c>
-      <c r="E186" s="90" t="s">
-        <v>623</v>
-      </c>
       <c r="F186" s="90" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -12410,54 +12771,54 @@
         <v>122</v>
       </c>
       <c r="E187" s="90" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F187" s="90" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="28" t="s">
+        <v>624</v>
+      </c>
+      <c r="E188" s="90" t="s">
         <v>625</v>
       </c>
-      <c r="E188" s="90" t="s">
-        <v>626</v>
-      </c>
       <c r="F188" s="90" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="E189" s="90" t="s">
         <v>627</v>
       </c>
-      <c r="E189" s="90" t="s">
-        <v>628</v>
-      </c>
       <c r="F189" s="90" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="E190" s="90" t="s">
         <v>629</v>
       </c>
-      <c r="E190" s="90" t="s">
-        <v>630</v>
-      </c>
       <c r="F190" s="90" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="28" t="s">
+        <v>630</v>
+      </c>
+      <c r="E191" s="90" t="s">
         <v>631</v>
       </c>
-      <c r="E191" s="90" t="s">
-        <v>632</v>
-      </c>
       <c r="F191" s="90" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -12465,164 +12826,164 @@
         <v>151</v>
       </c>
       <c r="E192" s="90" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F192" s="90" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="28" t="s">
+        <v>633</v>
+      </c>
+      <c r="E193" s="90" t="s">
         <v>634</v>
       </c>
-      <c r="E193" s="90" t="s">
-        <v>635</v>
-      </c>
       <c r="F193" s="90" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="28" t="s">
+        <v>635</v>
+      </c>
+      <c r="E194" s="90" t="s">
         <v>636</v>
       </c>
-      <c r="E194" s="90" t="s">
-        <v>637</v>
-      </c>
       <c r="F194" s="90" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="28" t="s">
+        <v>637</v>
+      </c>
+      <c r="E195" s="90" t="s">
         <v>638</v>
       </c>
-      <c r="E195" s="90" t="s">
-        <v>639</v>
-      </c>
       <c r="F195" s="90" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="28" t="s">
+        <v>639</v>
+      </c>
+      <c r="E196" s="90" t="s">
         <v>640</v>
       </c>
-      <c r="E196" s="90" t="s">
-        <v>641</v>
-      </c>
       <c r="F196" s="90" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="28" t="s">
+        <v>641</v>
+      </c>
+      <c r="E197" s="90" t="s">
         <v>642</v>
       </c>
-      <c r="E197" s="90" t="s">
-        <v>643</v>
-      </c>
       <c r="F197" s="90" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="28" t="s">
+        <v>643</v>
+      </c>
+      <c r="E198" s="90" t="s">
         <v>644</v>
       </c>
-      <c r="E198" s="90" t="s">
-        <v>645</v>
-      </c>
       <c r="F198" s="90" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="28" t="s">
+        <v>645</v>
+      </c>
+      <c r="E199" s="90" t="s">
         <v>646</v>
       </c>
-      <c r="E199" s="90" t="s">
-        <v>647</v>
-      </c>
       <c r="F199" s="90" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="28" t="s">
+        <v>647</v>
+      </c>
+      <c r="E200" s="90" t="s">
         <v>648</v>
       </c>
-      <c r="E200" s="90" t="s">
-        <v>649</v>
-      </c>
       <c r="F200" s="90" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="28" t="s">
+        <v>649</v>
+      </c>
+      <c r="E201" s="90" t="s">
         <v>650</v>
       </c>
-      <c r="E201" s="90" t="s">
-        <v>651</v>
-      </c>
       <c r="F201" s="90" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="E202" s="90" t="s">
         <v>652</v>
       </c>
-      <c r="E202" s="90" t="s">
-        <v>653</v>
-      </c>
       <c r="F202" s="90" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="28" t="s">
+        <v>653</v>
+      </c>
+      <c r="E203" s="90" t="s">
         <v>654</v>
       </c>
-      <c r="E203" s="90" t="s">
-        <v>655</v>
-      </c>
       <c r="F203" s="90" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="E204" s="90" t="s">
         <v>656</v>
       </c>
-      <c r="E204" s="90" t="s">
-        <v>657</v>
-      </c>
       <c r="F204" s="90" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="E205" s="90" t="s">
         <v>658</v>
       </c>
-      <c r="E205" s="90" t="s">
-        <v>659</v>
-      </c>
       <c r="F205" s="90" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="E206" s="90" t="s">
         <v>660</v>
       </c>
-      <c r="E206" s="90" t="s">
-        <v>661</v>
-      </c>
       <c r="F206" s="90" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -12668,24 +13029,24 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="98" t="s">
-        <v>250</v>
-      </c>
       <c r="C1" s="99" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C2" s="138" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D2">
         <v>1.48</v>
@@ -12693,10 +13054,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D3">
         <v>1.8</v>
@@ -12704,10 +13065,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D4">
         <v>0.99</v>
@@ -12715,10 +13076,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>665</v>
+      </c>
+      <c r="C5" t="s">
         <v>666</v>
-      </c>
-      <c r="C5" t="s">
-        <v>667</v>
       </c>
       <c r="D5">
         <v>1.75</v>
@@ -12726,10 +13087,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>667</v>
+      </c>
+      <c r="C6" t="s">
         <v>668</v>
-      </c>
-      <c r="C6" t="s">
-        <v>669</v>
       </c>
       <c r="D6">
         <v>1.1000000000000001</v>
@@ -12737,10 +13098,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D7">
         <v>2.34</v>
@@ -12748,26 +13109,26 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>670</v>
+      </c>
+      <c r="C8" t="s">
         <v>671</v>
-      </c>
-      <c r="C8" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>672</v>
+      </c>
+      <c r="C9" t="s">
         <v>673</v>
-      </c>
-      <c r="C9" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
+        <v>674</v>
+      </c>
+      <c r="C10" t="s">
         <v>675</v>
-      </c>
-      <c r="C10" t="s">
-        <v>676</v>
       </c>
     </row>
   </sheetData>
@@ -12786,24 +13147,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="207" t="s">
-        <v>677</v>
-      </c>
-      <c r="B1" s="207"/>
+      <c r="A1" s="232" t="s">
+        <v>676</v>
+      </c>
+      <c r="B1" s="232"/>
       <c r="C1" s="139"/>
       <c r="D1" s="139"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="140" t="s">
+        <v>677</v>
+      </c>
+      <c r="B2" s="141" t="s">
         <v>678</v>
-      </c>
-      <c r="B2" s="141" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="142" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B3" s="143">
         <v>850</v>
@@ -12811,7 +13172,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="144" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B4" s="145">
         <v>850</v>
@@ -12819,7 +13180,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="144" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B5" s="145">
         <v>300</v>
@@ -12827,7 +13188,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="144" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B6" s="145">
         <v>1800</v>
@@ -12835,7 +13196,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="144" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B7" s="145">
         <v>100</v>
@@ -12843,7 +13204,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="144" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B8" s="145">
         <v>50</v>
@@ -12851,7 +13212,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="144" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B9" s="145">
         <v>600</v>
@@ -12859,7 +13220,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="144" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B10" s="145">
         <v>250</v>
@@ -12867,7 +13228,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="146" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B11" s="147">
         <v>100</v>
@@ -12894,21 +13255,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="208" t="s">
+      <c r="A1" s="233" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="208"/>
-      <c r="C1" s="208"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
     </row>
     <row r="2" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="148" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="149" t="s">
         <v>249</v>
       </c>
-      <c r="B2" s="149" t="s">
-        <v>250</v>
-      </c>
       <c r="C2" s="150" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -13199,10 +13560,10 @@
     </row>
     <row r="31" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="154" t="s">
+        <v>599</v>
+      </c>
+      <c r="B31" s="168" t="s">
         <v>600</v>
-      </c>
-      <c r="B31" s="168" t="s">
-        <v>601</v>
       </c>
       <c r="C31" s="169"/>
     </row>
@@ -13295,16 +13656,18 @@
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="154" t="s">
         <v>178</v>
       </c>
       <c r="B41" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="173"/>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="173" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="154" t="s">
         <v>185</v>
       </c>
@@ -13313,7 +13676,7 @@
       </c>
       <c r="C42" s="173"/>
     </row>
-    <row r="43" spans="1:3" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="154" t="s">
         <v>187</v>
       </c>
@@ -13491,7 +13854,184 @@
         <v>242</v>
       </c>
       <c r="C61" s="184" t="s">
-        <v>604</v>
+        <v>170</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{016B98ED-C8D0-4940-8589-54630AB7B4CE}">
+  <sheetPr codeName="Tabelle6"/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="55.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="233" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+    </row>
+    <row r="2" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="148" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="149" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="150" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="151" t="s">
+        <v>822</v>
+      </c>
+      <c r="B3" s="152" t="s">
+        <v>839</v>
+      </c>
+      <c r="C3" s="153" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="154" t="s">
+        <v>787</v>
+      </c>
+      <c r="B4" s="155" t="s">
+        <v>840</v>
+      </c>
+      <c r="C4" s="156" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="155" t="s">
+        <v>841</v>
+      </c>
+      <c r="C5" s="156" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="151" t="s">
+        <v>834</v>
+      </c>
+      <c r="B6" s="199" t="s">
+        <v>833</v>
+      </c>
+      <c r="C6" s="193" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="200" t="s">
+        <v>838</v>
+      </c>
+      <c r="B7" s="201" t="s">
+        <v>837</v>
+      </c>
+      <c r="C7" s="204" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="151" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="196" t="s">
+        <v>842</v>
+      </c>
+      <c r="C8" s="197" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="151" t="s">
+        <v>824</v>
+      </c>
+      <c r="B9" s="194" t="s">
+        <v>823</v>
+      </c>
+      <c r="C9" s="153"/>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="200" t="s">
+        <v>826</v>
+      </c>
+      <c r="B10" s="202" t="s">
+        <v>825</v>
+      </c>
+      <c r="C10" s="203"/>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="200" t="s">
+        <v>828</v>
+      </c>
+      <c r="B11" s="202" t="s">
+        <v>827</v>
+      </c>
+      <c r="C11" s="203" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="151" t="s">
+        <v>836</v>
+      </c>
+      <c r="B12" s="195" t="s">
+        <v>835</v>
+      </c>
+      <c r="C12" s="198" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="154" t="s">
+        <v>830</v>
+      </c>
+      <c r="B13" s="180" t="s">
+        <v>829</v>
+      </c>
+      <c r="C13" s="181" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="154" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" s="180" t="s">
+        <v>831</v>
+      </c>
+      <c r="C14" s="181" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="182" t="s">
+        <v>792</v>
+      </c>
+      <c r="B15" s="183" t="s">
+        <v>832</v>
+      </c>
+      <c r="C15" s="184" t="s">
+        <v>844</v>
       </c>
     </row>
   </sheetData>
